--- a/data/questions/verbal_difficult.xlsx
+++ b/data/questions/verbal_difficult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="377">
   <si>
     <t>question_id</t>
   </si>
@@ -317,366 +317,996 @@
   </si>
   <si>
     <t>VD90</t>
+  </si>
+  <si>
+    <t>VD91</t>
+  </si>
+  <si>
+    <t>VD92</t>
+  </si>
+  <si>
+    <t>VD93</t>
+  </si>
+  <si>
+    <t>VD94</t>
+  </si>
+  <si>
+    <t>VD95</t>
+  </si>
+  <si>
+    <t>VD96</t>
+  </si>
+  <si>
+    <t>VD97</t>
+  </si>
+  <si>
+    <t>VD98</t>
+  </si>
+  <si>
+    <t>VD99</t>
+  </si>
+  <si>
+    <t>VD100</t>
+  </si>
+  <si>
+    <t>VD101</t>
+  </si>
+  <si>
+    <t>VD102</t>
+  </si>
+  <si>
+    <t>VD103</t>
+  </si>
+  <si>
+    <t>VD104</t>
+  </si>
+  <si>
+    <t>VD105</t>
+  </si>
+  <si>
+    <t>VD106</t>
+  </si>
+  <si>
+    <t>VD107</t>
+  </si>
+  <si>
+    <t>VD108</t>
+  </si>
+  <si>
+    <t>VD109</t>
+  </si>
+  <si>
+    <t>VD110</t>
+  </si>
+  <si>
+    <t>VD111</t>
+  </si>
+  <si>
+    <t>VD112</t>
+  </si>
+  <si>
+    <t>VD113</t>
+  </si>
+  <si>
+    <t>VD114</t>
+  </si>
+  <si>
+    <t>VD115</t>
+  </si>
+  <si>
+    <t>VD116</t>
+  </si>
+  <si>
+    <t>VD117</t>
+  </si>
+  <si>
+    <t>VD118</t>
+  </si>
+  <si>
+    <t>VD119</t>
+  </si>
+  <si>
+    <t>VD120</t>
+  </si>
+  <si>
+    <t>VD121</t>
+  </si>
+  <si>
+    <t>VD122</t>
+  </si>
+  <si>
+    <t>VD123</t>
+  </si>
+  <si>
+    <t>VD124</t>
+  </si>
+  <si>
+    <t>VD125</t>
+  </si>
+  <si>
+    <t>VD126</t>
+  </si>
+  <si>
+    <t>VD127</t>
+  </si>
+  <si>
+    <t>VD128</t>
+  </si>
+  <si>
+    <t>VD129</t>
+  </si>
+  <si>
+    <t>VD130</t>
+  </si>
+  <si>
+    <t>VD131</t>
+  </si>
+  <si>
+    <t>VD132</t>
+  </si>
+  <si>
+    <t>VD133</t>
+  </si>
+  <si>
+    <t>VD134</t>
+  </si>
+  <si>
+    <t>VD135</t>
+  </si>
+  <si>
+    <t>VD136</t>
+  </si>
+  <si>
+    <t>VD137</t>
+  </si>
+  <si>
+    <t>VD138</t>
+  </si>
+  <si>
+    <t>VD139</t>
+  </si>
+  <si>
+    <t>VD140</t>
+  </si>
+  <si>
+    <t>VD141</t>
+  </si>
+  <si>
+    <t>VD142</t>
+  </si>
+  <si>
+    <t>VD143</t>
+  </si>
+  <si>
+    <t>VD144</t>
+  </si>
+  <si>
+    <t>VD145</t>
+  </si>
+  <si>
+    <t>VD146</t>
+  </si>
+  <si>
+    <t>VD147</t>
+  </si>
+  <si>
+    <t>VD148</t>
+  </si>
+  <si>
+    <t>VD149</t>
+  </si>
+  <si>
+    <t>VD150</t>
+  </si>
+  <si>
+    <t>VD151</t>
+  </si>
+  <si>
+    <t>VD152</t>
+  </si>
+  <si>
+    <t>VD153</t>
+  </si>
+  <si>
+    <t>VD154</t>
+  </si>
+  <si>
+    <t>VD155</t>
+  </si>
+  <si>
+    <t>VD156</t>
+  </si>
+  <si>
+    <t>VD157</t>
+  </si>
+  <si>
+    <t>VD158</t>
+  </si>
+  <si>
+    <t>VD159</t>
+  </si>
+  <si>
+    <t>VD160</t>
+  </si>
+  <si>
+    <t>VD161</t>
+  </si>
+  <si>
+    <t>VD162</t>
+  </si>
+  <si>
+    <t>VD163</t>
+  </si>
+  <si>
+    <t>VD164</t>
+  </si>
+  <si>
+    <t>VD165</t>
+  </si>
+  <si>
+    <t>VD166</t>
+  </si>
+  <si>
+    <t>VD167</t>
+  </si>
+  <si>
+    <t>VD168</t>
+  </si>
+  <si>
+    <t>VD169</t>
+  </si>
+  <si>
+    <t>VD170</t>
+  </si>
+  <si>
+    <t>VD171</t>
+  </si>
+  <si>
+    <t>VD172</t>
+  </si>
+  <si>
+    <t>VD173</t>
+  </si>
+  <si>
+    <t>VD174</t>
+  </si>
+  <si>
+    <t>VD175</t>
+  </si>
+  <si>
+    <t>VD176</t>
+  </si>
+  <si>
+    <t>VD177</t>
+  </si>
+  <si>
+    <t>VD178</t>
+  </si>
+  <si>
+    <t>VD179</t>
+  </si>
+  <si>
+    <t>VD180</t>
+  </si>
+  <si>
+    <t>**Passage:** Permission for a residential extension is generally granted where the proposal complies with the local design code.
+**Statement:** Local design codes are reviewed by the planning authority every five years.</t>
+  </si>
+  <si>
+    <t>**Passage:** Mediation must be attempted before any party initiates court proceedings, except where the dispute concerns urgent injunctive relief.
+**Statement:** Save for urgent injunction matters, parties must try mediation before going to court.</t>
+  </si>
+  <si>
+    <t>**Passage:** Members of the public attending a planning hearing may speak for up to three minutes each, although the chair retains discretion over the order in which speakers are called.
+**Statement:** The order in which members of the public speak at a planning hearing is determined by the chair.</t>
+  </si>
+  <si>
+    <t>**Passage:** The whistleblowing hotline operates twenty-four hours a day, seven days a week, with reports treated as confidential.
+**Statement:** A worker can use the whistleblowing hotline outside normal office hours.</t>
+  </si>
+  <si>
+    <t>**Passage:** Bondholders representing at least twenty-five per cent of the outstanding principal may accelerate repayment if the issuer fails to remedy a covenant breach within the cure period.
+**Statement:** Acceleration of bond repayment requires the support of a minority of bondholders.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where multiple people wish to speak on the same item, the chair may direct that one representative speak on behalf of others.
+**Statement:** The chair has the authority to consolidate multiple speakers on the same item.</t>
+  </si>
+  <si>
+    <t>**Passage:** The board may approve capital expenditure on its own authority where the proposal is below the standard threshold. Proposals classified as strategic require shareholder approval regardless of value.
+**Statement:** A proposal classified as strategic but below the standard threshold can be approved by the board acting alone.</t>
+  </si>
+  <si>
+    <t>**Passage:** The exclusive European rights granted under the licence cover the entire European market.
+**Statement:** The exclusive rights apply to all twenty-seven EU member states.</t>
+  </si>
+  <si>
+    <t>**Passage:** The new safety protocol applies to all production lines except those handling pharmaceutical-grade materials, which remain under the existing protocol.
+**Statement:** A line handling pharmaceutical-grade materials must follow the new safety protocol.</t>
+  </si>
+  <si>
+    <t>**Passage:** The franchise grants exclusive rights for an initial five-year term. Renewal requires written notice at least six months before expiry, in addition to performance benchmarks being met.
+**Statement:** A franchisee who has met all performance benchmarks but failed to give six months' notice loses the right to renew.</t>
+  </si>
+  <si>
+    <t>**Passage:** Members of the public attending a planning hearing may speak for up to three minutes each. Where multiple people wish to speak on the same item, the chair may direct that one representative speak on behalf of others.
+**Statement:** Members of the public may always speak individually on every item.</t>
+  </si>
+  <si>
+    <t>**Passage:** A first proven offence of plagiarism results in a mark of zero for the affected assessment, with no opportunity to resubmit.
+**Statement:** A student with a first plagiarism offence cannot improve their grade for that piece of work by resubmitting.</t>
+  </si>
+  <si>
+    <t>**Passage:** The sports and social club receives an annual subsidy from the company.
+**Statement:** The annual subsidy has remained unchanged for at least five years.</t>
+  </si>
+  <si>
+    <t>**Passage:** The contract may be terminated for cause by either party with immediate effect. Termination without cause requires three months' written notice. Where the contract has been in force for more than three years, an additional month of notice is required for termination without cause.
+**Statement:** A contract in its second year can be terminated without cause with three months' notice.</t>
+  </si>
+  <si>
+    <t>**Passage:** Members completing more than sixty hours of CPD per year may carry forward up to ten hours to the following year.
+**Statement:** A member completing exactly sixty hours can carry forward hours.</t>
+  </si>
+  <si>
+    <t>**Passage:** Residential developments of ten or more units must allocate a portion of units to affordable housing.
+**Statement:** Affordable housing must be provided as social rent rather than shared ownership.</t>
+  </si>
+  <si>
+    <t>**Passage:** Spectrum efficiency reviews are conducted two years before licence expiry.
+**Statement:** The spectrum efficiency review is held immediately after the licence has expired.</t>
+  </si>
+  <si>
+    <t>**Passage:** Statutory sick pay begins on the fourth day of absence for workplace injuries.
+**Statement:** Statutory sick pay is paid at a rate equivalent to the worker's full daily salary.</t>
+  </si>
+  <si>
+    <t>**Passage:** Subrogation gives the insurer the right to recover from a third party any sum paid out to the insured.
+**Statement:** Subrogation rights apply only after the insured has consented in writing to the insurer pursuing the recovery.</t>
+  </si>
+  <si>
+    <t>**Passage:** The whistleblowing policy protects any worker who, in good faith, reports suspected wrongdoing. Reports made maliciously or in bad faith are not covered by these protections.
+**Statement:** A worker who maliciously fabricates an allegation is protected from disciplinary action.</t>
+  </si>
+  <si>
+    <t>**Passage:** Affordable housing contributions can be made on-site or as a financial contribution where on-site delivery is impracticable.
+**Statement:** A financial contribution in lieu of on-site delivery is permitted in all circumstances.</t>
+  </si>
+  <si>
+    <t>**Passage:** Editorial decisions on news content are made by the editor-in-chief, in consultation with the news desk.
+**Statement:** The editor-in-chief is appointed by the board of directors.</t>
+  </si>
+  <si>
+    <t>**Passage:** Workers who suffer an injury at work are entitled to statutory sick pay from the fourth day of absence.
+**Statement:** Statutory sick pay for a workplace injury does not begin on the first day of absence.</t>
+  </si>
+  <si>
+    <t>**Passage:** Residential developments of ten or more units must allocate a portion of units to affordable housing.
+**Statement:** A development of eight units must include affordable housing.</t>
+  </si>
+  <si>
+    <t>**Passage:** The professional standards committee may impose sanctions ranging from a written warning to permanent expulsion.
+**Statement:** The committee can impose a financial fine on a member found to have committed misconduct.</t>
+  </si>
+  <si>
+    <t>**Passage:** The recycling scheme covers paper, cardboard, plastics, and glass.
+**Statement:** The recycling scheme reduced waste sent to landfill by forty per cent in its first year.</t>
+  </si>
+  <si>
+    <t>**Passage:** Holdings between the disclosure threshold and the substantial threshold must be disclosed to the company.
+**Statement:** Companies are required to maintain a public register of all shareholders above the disclosure threshold.</t>
+  </si>
+  <si>
+    <t>**Passage:** NHS goods and services contracts above a defined threshold must follow public procurement regulations. Contracts below the threshold remain subject to the trust's internal financial procedures.
+**Statement:** A services contract below the threshold is exempt from all procurement-related rules.</t>
+  </si>
+  <si>
+    <t>**Passage:** Staff may borrow up to five items at a time from the company library.
+**Statement:** Library items can be renewed online once before being returned.</t>
+  </si>
+  <si>
+    <t>**Passage:** There are four trained first aid officers on duty during working hours.
+**Statement:** More than half of the first aid officers are female.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where the licence holder fails to renew before expiry, abstraction must cease immediately and cannot resume until a new licence is granted.
+**Statement:** A licence holder whose licence has expired and not been renewed cannot legally continue abstracting water.</t>
+  </si>
+  <si>
+    <t>**Passage:** Tenancy deposits must be lodged with an approved deposit protection scheme within thirty days of receipt.
+**Statement:** A landlord who receives a deposit on the first of the month must protect it before the end of that month.</t>
+  </si>
+  <si>
+    <t>**Passage:** The audit committee is responsible for reviewing the integrity of the financial statements and overseeing the relationship with the external auditor.
+**Statement:** The audit committee meets at least four times per year.</t>
+  </si>
+  <si>
+    <t>**Passage:** Insurance subrogation gives the insurer the right to recover from a third party any sum paid out to the insured for losses caused by that party.
+**Statement:** An insurer that has paid a claim cannot pursue the party that caused the loss.</t>
+  </si>
+  <si>
+    <t>**Passage:** The carbon offset scheme operates as a voluntary supplement to mandatory emissions reductions, with credits purchased to offset only those emissions that cannot be eliminated through operational improvements.
+**Statement:** Offset credits are intended for residual emissions that cannot otherwise be reduced.</t>
+  </si>
+  <si>
+    <t>**Passage:** Bond covenants require maintenance of a leverage ratio. A breach triggers a cure period during which the issuer may remedy the breach.
+**Statement:** A covenant breach immediately entitles bondholders to demand repayment.</t>
+  </si>
+  <si>
+    <t>**Passage:** Workers who suffer an injury at work are entitled to statutory sick pay from the fourth day of absence.
+**Statement:** A worker absent for two days due to a workplace injury receives statutory sick pay.</t>
+  </si>
+  <si>
+    <t>**Passage:** Government bonds maturing in more than ten years are classified as long-dated. Bonds maturing in five to ten years are classified as medium-dated.
+**Statement:** A bond maturing in eight years is classified as long-dated.</t>
+  </si>
+  <si>
+    <t>**Passage:** Long service awards are presented after ten, twenty, and thirty years of continuous service.
+**Statement:** Long service awards include a financial gift of five hundred pounds.</t>
   </si>
   <si>
     <t>**Passage:** Tenants whose rent is more than two months in arrears may be served with a notice to quit. The notice period is one month if the tenancy is under three years old, and two months otherwise.
 **Statement:** A tenant in their fifth year of occupation who has not paid rent for three months must be given two months' notice.</t>
   </si>
   <si>
-    <t>**Passage:** The board may approve capital expenditure on its own authority where the proposal is below the standard threshold. Proposals at or above the threshold require a recommendation from the audit committee. Proposals classified as strategic require shareholder approval regardless of value.
-**Statement:** A proposal classified as strategic but below the standard threshold can be approved by the board acting alone.</t>
-  </si>
-  <si>
-    <t>**Passage:** Under the lease accounting standard, all leases exceeding 12 months must be recognised on the balance sheet, unless the underlying asset is of low value.
-**Statement:** A 24-month lease of a low-value asset must be recognised on the balance sheet.</t>
-  </si>
-  <si>
-    <t>**Passage:** Short-term leases of 12 months or less may be expensed on a straight-line basis without balance sheet recognition.
-**Statement:** A 14-month lease qualifies as a short-term lease.</t>
-  </si>
-  <si>
-    <t>**Passage:** The new safety protocol applies to all production lines except those handling pharmaceutical-grade materials, which remain under the existing protocol. Lines that have been certified under both protocols may operate under either.
-**Statement:** A line handling pharmaceutical-grade materials is required to follow the new safety protocol.</t>
-  </si>
-  <si>
-    <t>**Passage:** Intercompany transactions above £500,000 require formal transfer pricing documentation. Transactions involving intangible assets require a full valuation report regardless of size.
-**Statement:** A £200,000 transaction involving software licences requires a full valuation report.</t>
-  </si>
-  <si>
-    <t>**Passage:** Visa applications submitted in person are processed within two working weeks. Postal applications take up to three working weeks. Online applications are typically processed faster, except where additional documentation is requested, in which case the timeline restarts.
-**Statement:** An online application that triggers a documentation request will be completed within the original online processing time.</t>
-  </si>
-  <si>
-    <t>**Passage:** Refunds for cancelled flights are issued in the original form of payment. Where the original payment method is no longer available, the refund is issued as a travel voucher valid for twelve months. Vouchers may be used for any flight operated by the airline or its codeshare partners.
+    <t>**Passage:** Failure to register an installation between defined emission bands constitutes an offence under the regulations.
+**Statement:** Failure to register an installation in the relevant band has no regulatory consequence.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where the dispute concerns urgent injunctive relief, the parties may bypass the standard mediation requirement that would otherwise apply.
+**Statement:** An urgent injunction case is exempt from the usual obligation to attempt mediation first.</t>
+  </si>
+  <si>
+    <t>**Passage:** NHS goods and services contracts above a defined threshold must follow public procurement regulations.
+**Statement:** The procurement threshold is updated every two years.</t>
+  </si>
+  <si>
+    <t>**Passage:** A settlement agreement is binding only if the employee has received independent legal advice before signing.
+**Statement:** The settlement bars the employee from working for competitors for twelve months.</t>
+  </si>
+  <si>
+    <t>**Passage:** A revocation of a licence requires a public hearing where the licence holder may make representations.
+**Statement:** A licence may be revoked without giving the licence holder an opportunity to be heard.</t>
+  </si>
+  <si>
+    <t>**Passage:** Tenancy deposits must be lodged with an approved deposit protection scheme within thirty days of receipt. Failure to comply may result in the tenant being awarded up to three times the deposit amount as compensation, at the court's discretion.
+**Statement:** A landlord who fails to protect a deposit will automatically pay three times the deposit as compensation.</t>
+  </si>
+  <si>
+    <t>**Passage:** Casual clothing is permitted on Fridays for all office-based staff.
+**Statement:** Casual clothing is permitted on Wednesdays for those working from home.</t>
+  </si>
+  <si>
+    <t>**Passage:** The pension scheme has assets below its liabilities, indicating a funding shortfall.
+**Statement:** The pension scheme is currently in surplus.</t>
+  </si>
+  <si>
+    <t>**Passage:** Decommissioning funds are held in ring-fenced trusts and may not be used for any purpose other than decommissioning.
+**Statement:** An operator cannot draw on the decommissioning fund to cover unrelated business expenses.</t>
+  </si>
+  <si>
+    <t>**Passage:** Bondholders representing at least twenty-five per cent of the outstanding principal may accelerate repayment.
+**Statement:** Bondholders must hold their position for twelve months before they can vote on acceleration.</t>
+  </si>
+  <si>
+    <t>**Passage:** Permission for a residential extension is generally granted where the proposal complies with the local design code.
+**Statement:** An extension that breaches the local design code is unlikely to receive permission as a matter of routine.</t>
+  </si>
+  <si>
+    <t>**Passage:** Inventions created by academic staff in the course of their employment vest in the university.
+**Statement:** Academic staff personally own inventions they create as part of their job.</t>
+  </si>
+  <si>
+    <t>**Passage:** Shareholder resolutions are categorised as ordinary, special, or unanimous, each with its own approval threshold.
+**Statement:** A resolution approved unanimously by every shareholder qualifies as a special resolution.</t>
+  </si>
+  <si>
+    <t>**Passage:** The mortgage is offered at a variable rate. The lender may change the rate with thirty days' written notice to the borrower.
+**Statement:** The lender can change the rate without informing the borrower.</t>
+  </si>
+  <si>
+    <t>**Passage:** The collective bargaining agreement requires thirty days' notice before any industrial action.
+**Statement:** A two-week notice of industrial action complies with the agreement.</t>
+  </si>
+  <si>
+    <t>**Passage:** The whistleblowing hotline is available twenty-four hours a day, seven days a week.
+**Statement:** The whistleblowing hotline is operated by an external provider rather than internal staff.</t>
+  </si>
+  <si>
+    <t>**Passage:** All visitors must show a form of photographic identification at reception.
+**Statement:** Visitors must wear a face covering at all times in the building.</t>
+  </si>
+  <si>
+    <t>**Passage:** Disputes are resolved first through informal discussion. If informal resolution fails, the matter is referred to mediation. Mediation must be attempted before any party initiates court proceedings, except where the dispute concerns urgent injunctive relief.
+**Statement:** A party seeking an emergency injunction may apply directly to the court without first attempting mediation.</t>
+  </si>
+  <si>
+    <t>**Passage:** Health insurance is provided to all permanent employees who have completed their six-month probation.
+**Statement:** Health insurance premiums are paid in full by the company.</t>
+  </si>
+  <si>
+    <t>**Passage:** Politically exposed persons (PEPs) are subject to enhanced due diligence regardless of transaction size. PEPs include senior public officials, their immediate family members, and known close associates.
+**Statement:** A close associate of a senior public official is treated as a PEP for due diligence purposes.</t>
+  </si>
+  <si>
+    <t>**Passage:** Personal data breaches that pose a risk must be reported to the supervisory authority within seventy-two hours.
+**Statement:** Most data breaches occur due to human error.</t>
+  </si>
+  <si>
+    <t>**Passage:** The licensing authority may issue, vary, or revoke licences. Revocation requires a public hearing where the licence holder may make representations.
+**Statement:** A licence holder is entitled to make their case before a revocation decision becomes final.</t>
+  </si>
+  <si>
+    <t>**Passage:** Restaurants and cafés serving non-pre-packaged food are exempt from the food labelling regulation that requires energy-value display on packaged products.
+**Statement:** A café selling pastries made on the premises must label energy values for each pastry.</t>
+  </si>
+  <si>
+    <t>**Passage:** Anticipated contract losses are recognised immediately in the income statement.
+**Statement:** Anticipated losses on a construction contract are spread over the remaining life of the contract.</t>
+  </si>
+  <si>
+    <t>**Passage:** Underspent grant funds must be returned to the funder unless a no-cost extension is agreed in writing.
+**Statement:** An institution can retain underspent grant funds without any formal process.</t>
+  </si>
+  <si>
+    <t>**Passage:** Office temperatures are maintained between nineteen and twenty-three degrees Celsius.
+**Statement:** Employees report higher productivity when temperatures are at the lower end of the range.</t>
+  </si>
+  <si>
+    <t>**Passage:** The audit committee is responsible for reviewing the integrity of the financial statements and overseeing the relationship with the external auditor.
+**Statement:** Oversight of the external auditor sits with the audit committee.</t>
+  </si>
+  <si>
+    <t>**Passage:** The carbon offset scheme operates as a voluntary supplement to mandatory emissions reductions.
+**Statement:** Most major corporations participate in the voluntary carbon offset scheme.</t>
+  </si>
+  <si>
+    <t>**Passage:** The media plurality framework caps newspaper circulation share and television audience share separately.
+**Statement:** Fines for media plurality breaches are capped at ten per cent of annual revenue.</t>
+  </si>
+  <si>
+    <t>**Passage:** Failure to register an installation between five and twenty tonnes constitutes an offence.
+**Statement:** Failure to register results in an automatic financial penalty.</t>
+  </si>
+  <si>
+    <t>**Passage:** Strict liability applies — the claimant does not need to prove negligence to succeed.
+**Statement:** A claimant under this regime can win without showing the defendant acted negligently.</t>
+  </si>
+  <si>
+    <t>**Passage:** Local authorities have a power, but not a duty, to undertake coastal protection works.
+**Statement:** A local authority cannot be legally compelled by a property owner to carry out coastal works.</t>
+  </si>
+  <si>
+    <t>**Passage:** The grant requires that at least seventy per cent of funds be spent on direct research and no more than twenty per cent on indirect costs.
+**Statement:** The principal investigator may allocate up to thirty per cent of the grant to indirect costs.</t>
+  </si>
+  <si>
+    <t>**Passage:** The exclusive European rights granted under the licence are valid for the remainder of the patent term.
+**Statement:** The licensee may sub-license rights to third parties within Europe.</t>
+  </si>
+  <si>
+    <t>**Passage:** Refunds for cancelled flights are issued in the original form of payment. Where the original payment method is no longer available, the refund is issued as a travel voucher.
 **Statement:** A passenger whose original credit card has been cancelled will receive a cash refund.</t>
   </si>
   <si>
-    <t>**Passage:** The professional indemnity policy has an aggregate limit of £5 million per year and a per-claim excess of £25,000.
-**Statement:** The insurer would pay the full amount of any successful claim.</t>
-  </si>
-  <si>
-    <t>**Passage:** The patent licence grants exclusive rights in Europe and non-exclusive rights in Asia-Pacific.
-**Statement:** The exclusive European rights cover all 27 EU member states.</t>
-  </si>
-  <si>
-    <t>**Passage:** The professional standards committee may impose sanctions ranging from a written warning to permanent expulsion from the register. Expulsion is reserved for serious or repeated misconduct. The decision must be notified in writing within fourteen days of the hearing. An appeal may be lodged within thirty days of notification.
-**Statement:** A member who is expelled loses the right to appeal once thirty days have passed since notification.</t>
+    <t>**Passage:** Politically exposed persons (PEPs) are subject to enhanced due diligence regardless of transaction size.
+**Statement:** A small transaction with a PEP requires only standard due diligence.</t>
+  </si>
+  <si>
+    <t>**Passage:** Tenancies of two years or less may be terminated at the end of the term with one month's notice. For tenancies of more than two years, longer notice is required.
+**Statement:** All agricultural tenancies can be ended with one month's notice.</t>
+  </si>
+  <si>
+    <t>**Passage:** Shareholders holding a substantial stake are required to disclose their holding to the market.
+**Statement:** A shareholder with a holding above the substantial threshold may keep their position confidential.</t>
+  </si>
+  <si>
+    <t>**Passage:** The new safety protocol applies to all production lines except those handling pharmaceutical-grade materials, which remain under the existing protocol.
+**Statement:** Lines that do not handle pharmaceutical-grade materials are governed by the new safety protocol.</t>
+  </si>
+  <si>
+    <t>**Passage:** The training programme consists of three phases: induction, supervised practice, and independent practice.
+**Statement:** Trainees who complete all three phases automatically qualify as full members of the profession.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where between twenty and ninety-nine redundancies are proposed, the minimum consultation period is thirty days.
+**Statement:** Eighty redundancies must be staggered evenly across the consultation period.</t>
+  </si>
+  <si>
+    <t>**Passage:** Failure to comply with the data protection regulations may result in fines of up to four per cent of global annual turnover.
+**Statement:** An organisation in breach of the regulations could face a financial penalty linked to its size.</t>
+  </si>
+  <si>
+    <t>**Passage:** Recycling bins are emptied every Wednesday by the local authority.
+**Statement:** Recycling collection charges are passed on to staff.</t>
+  </si>
+  <si>
+    <t>**Passage:** Permission for a residential extension is generally granted where the proposal complies with the local design code. Extensions in conservation areas require additional consideration of heritage impact. Where the property is listed, separate listed building consent is required in addition to planning permission.
+**Statement:** An extension to a listed property in a conservation area requires both listed building consent and consideration of heritage impact.</t>
+  </si>
+  <si>
+    <t>**Passage:** Tenants whose rent is more than two months in arrears may be served with a notice to quit.
+**Statement:** A landlord whose tenant pays partial rent each month, totalling less than full rent, can serve a notice to quit after six months.</t>
+  </si>
+  <si>
+    <t>**Passage:** Goods originating from FTA countries pay duty at a preferential rate.
+**Statement:** FTA preferential rates are reviewed annually by the trade ministry.</t>
+  </si>
+  <si>
+    <t>**Passage:** Revenue from maintenance contracts is recognised on a straight-line basis over the contract term.
+**Statement:** Maintenance contract revenue is spread evenly across the period of the contract.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 3 drugs require a prescription, although the prescription-writing rules are less stringent than for Schedule 2.
+**Statement:** A Schedule 3 drug can be dispensed without any prescription.</t>
+  </si>
+  <si>
+    <t>**Passage:** Wind turbines installed within eight hundred metres of a residential property require an additional acoustic assessment.
+**Statement:** Acoustic assessments must be conducted by independent acoustic engineers.</t>
+  </si>
+  <si>
+    <t>**Passage:** References confirm job title, dates of employment, and whether the employee left voluntarily.
+**Statement:** Reference letters are usually issued within five working days.</t>
+  </si>
+  <si>
+    <t>**Passage:** Pre-packaged food labelling must include energy values per one hundred grams.
+**Statement:** All restaurants must display calorie counts on their menus.</t>
+  </si>
+  <si>
+    <t>**Passage:** Right-to-buy eligibility requires three years' occupation as the only or principal home.
+**Statement:** A tenant with two years' occupation is eligible to buy.</t>
+  </si>
+  <si>
+    <t>**Passage:** Consumer credit advertisements must show the APR as prominently as any associated rate, where the advert includes any numerical interest or repayment figure.
+**Statement:** A credit advertisement containing only descriptive text and no numbers must show an APR.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 1 drug research requires a Home Office licence.
+**Statement:** Schedule 1 drug research is funded primarily by government grants.</t>
+  </si>
+  <si>
+    <t>**Passage:** Visa applications submitted in person are processed within two working weeks.
+**Statement:** In-person applications can only be made at designated consulate locations.</t>
+  </si>
+  <si>
+    <t>**Passage:** Holdings between the disclosure threshold and the substantial threshold must be disclosed to the company but not made public.
+**Statement:** All shareholdings above the disclosure threshold are made public.</t>
+  </si>
+  <si>
+    <t>**Passage:** Television audience share is subject to a regulatory cap.
+**Statement:** The audience share cap is measured by total viewing hours rather than reach.</t>
+  </si>
+  <si>
+    <t>**Passage:** Employers customarily contribute to the employee's legal fees, although this is not a legal requirement.
+**Statement:** Employers must pay the employee's legal fees as part of any settlement.</t>
+  </si>
+  <si>
+    <t>**Passage:** The vehicle inspection scheme tests roadworthiness on three criteria: brakes, lights, and tyres. A vehicle that fails one criterion is issued a warning notice.
+**Statement:** A vehicle with defective brakes alone will be impounded immediately.</t>
+  </si>
+  <si>
+    <t>**Passage:** Refunds for cancelled flights are issued in the original form of payment. Where the original payment method is no longer available, the refund is issued as a travel voucher valid for twelve months.
+**Statement:** A passenger whose original credit card has expired since paying may receive a travel voucher rather than a card refund.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 2 drugs require a full prescription written in ink, signed, and including the patient's name and address.
+**Statement:** Schedule 2 drug prescriptions are valid for twenty-eight days from the date of issue.</t>
+  </si>
+  <si>
+    <t>**Passage:** The mortgage carries an early repayment charge if repaid in full within the first three years.
+**Statement:** A borrower repaying after four years would incur an early repayment charge.</t>
+  </si>
+  <si>
+    <t>**Passage:** The anti-bribery policy prohibits facilitation payments even where they are customary or legally permitted in the local jurisdiction.
+**Statement:** Facilitation payments are banned even in jurisdictions where they are lawful.</t>
+  </si>
+  <si>
+    <t>**Passage:** First proven offences of plagiarism result in a mark of zero for the affected assessment.
+**Statement:** A first plagiarism offence results in failure of the entire module.</t>
+  </si>
+  <si>
+    <t>**Passage:** All new employees serve a six-month probationary period.
+**Statement:** New employees receive a salary review at the end of their probation.</t>
+  </si>
+  <si>
+    <t>**Passage:** Manufacturers are strictly liable for damage caused by defective products.
+**Statement:** A claimant must prove the manufacturer was negligent to succeed in a product liability claim.</t>
+  </si>
+  <si>
+    <t>**Passage:** Whistleblowing protections are available to any worker who, in good faith, reports suspected wrongdoing through approved channels.
+**Statement:** An employee acting honestly when they raise a concern is covered by whistleblowing protections.</t>
+  </si>
+  <si>
+    <t>**Passage:** Personal data breaches must be reported to the supervisory authority within seventy-two hours where the breach is likely to result in a risk to individuals' rights.
+**Statement:** All data breaches must be reported within seventy-two hours.</t>
+  </si>
+  <si>
+    <t>**Passage:** The clinical trial is conducted across multiple countries in line with the relevant ethical framework.
+**Statement:** The trial requires written informed consent from all participants.</t>
+  </si>
+  <si>
+    <t>**Passage:** The collective bargaining agreement requires thirty days' notice before any industrial action, and notice must specify the type of action and start date.
+**Statement:** A union taking industrial action must inform the employer in advance of what kind of action is planned.</t>
+  </si>
+  <si>
+    <t>**Passage:** Members of the public attending a planning hearing may speak for up to three minutes each.
+**Statement:** A member of the public who speaks for two and a half minutes is within the time limit.</t>
+  </si>
+  <si>
+    <t>**Passage:** Underspent grant funds must be returned to the funder unless a no-cost extension is agreed.
+**Statement:** Returns of unspent grant funds must be made within sixty days of grant end.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where the employee has been continuously employed for at least two years, dismissal must be for a fair reason and follow a fair procedure.
+**Statement:** An employee with thirty months' continuous service is entitled to a fair procedure on dismissal.</t>
+  </si>
+  <si>
+    <t>**Passage:** Aviation accidents must be reported to the safety authority within seventy-two hours.
+**Statement:** Aviation accidents may be reported up to a week after they occur and remain compliant.</t>
+  </si>
+  <si>
+    <t>**Passage:** Wind turbines installed within eight hundred metres of a residential property require an additional acoustic assessment.
+**Statement:** A wind turbine one kilometre from the nearest house requires an acoustic assessment.</t>
+  </si>
+  <si>
+    <t>**Passage:** Trainees must pass a competency assessment at the end of each phase before progressing to the next phase.
+**Statement:** Failing the assessment at the end of phase one prevents the trainee from starting phase two.</t>
+  </si>
+  <si>
+    <t>**Passage:** The vehicle inspection scheme tests roadworthiness on three criteria: brakes, lights, and tyres.
+**Statement:** Vehicle inspections are carried out by approved third-party providers rather than by the regulator.</t>
+  </si>
+  <si>
+    <t>**Passage:** The vehicle inspection scheme tests roadworthiness on three criteria: brakes, lights, and tyres. A vehicle that fails two or more criteria simultaneously is impounded immediately.
+**Statement:** A vehicle that fails the brakes and tyres tests at the same inspection will be impounded.</t>
+  </si>
+  <si>
+    <t>**Passage:** The right to buy scheme allows secure tenants of social housing to purchase their home at a discount. Eligibility requires the tenant to have occupied the property as their only or principal home for a minimum of three years.
+**Statement:** A tenant who has used the property as a holiday home for four years is not eligible to buy.</t>
+  </si>
+  <si>
+    <t>**Passage:** Editorial decisions on news content are made by the editor-in-chief, in consultation with the news desk. Sponsored content is the responsibility of the commercial director.
+**Statement:** The editor-in-chief is responsible for sponsored content.</t>
+  </si>
+  <si>
+    <t>**Passage:** Primary endpoint data is expected to be available approximately twenty-four months after enrolment closes.
+**Statement:** The trial will be completed within four years of starting enrolment.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 1 controlled drugs require a Home Office licence for any handling.
+**Statement:** A pharmacy can dispense Schedule 1 drugs to patients with a standard NHS prescription.</t>
+  </si>
+  <si>
+    <t>**Passage:** Self-plagiarism — submitting the same work for two assessments — is treated as a first offence regardless of any prior record.
+**Statement:** A student with two prior plagiarism offences who self-plagiarises is treated as a first offender for that incident.</t>
+  </si>
+  <si>
+    <t>**Passage:** Notification to affected individuals is required where the breach is likely to result in a high risk to their rights and freedoms.
+**Statement:** A breach posing a high risk to rights and freedoms triggers an obligation to inform the affected individuals.</t>
+  </si>
+  <si>
+    <t>**Passage:** Decommissioning funds are held in ring-fenced trusts and may not be used for any purpose other than decommissioning.
+**Statement:** The fund can be drawn upon to cover operational losses in difficult years.</t>
+  </si>
+  <si>
+    <t>**Passage:** Editorial decisions on news content are made by the editor-in-chief, in consultation with the news desk. Where there is disagreement between editorial and commercial functions, the publisher has final authority.
+**Statement:** The publisher's authority is decisive only in cases of disagreement between editorial and commercial sides.</t>
+  </si>
+  <si>
+    <t>**Passage:** The professional indemnity policy has a per-claim excess: the insured bears the first portion of every claim before the insurer responds.
+**Statement:** The insurer pays the full amount of any successful claim against the firm.</t>
+  </si>
+  <si>
+    <t>**Passage:** Local authorities have a power, but not a duty, to undertake coastal protection works.
+**Statement:** Local authorities employ a coastal protection engineer at every coastal location.</t>
+  </si>
+  <si>
+    <t>**Passage:** Members of the professional body must complete continuing professional development each year, of which a defined minimum proportion must be structured learning.
+**Statement:** A member who undertakes only informal, unstructured learning has not satisfied the annual CPD requirement.</t>
+  </si>
+  <si>
+    <t>**Passage:** Patients arriving at the urgent care centre are triaged based on the severity of their condition. Category 1 patients are seen immediately.
+**Statement:** A Category 1 patient is not made to wait before being seen.</t>
+  </si>
+  <si>
+    <t>**Passage:** A settlement agreement between an employer and employee is binding only if the employee has received independent legal advice from a relevant adviser before signing.
+**Statement:** An employee who signs without legal advice is bound by the settlement.</t>
+  </si>
+  <si>
+    <t>**Passage:** Splitting a contract artificially to fall below the procurement threshold is a breach regardless of individual contract values.
+**Statement:** Dividing a single large contract into smaller ones to avoid procurement is a permitted optimisation strategy.</t>
+  </si>
+  <si>
+    <t>**Passage:** Subrogation gives the insurer the right to recover from a third party any sum paid out to the insured for losses caused by that third party.
+**Statement:** An insurer who has paid out on a claim may pursue the party responsible for the loss.</t>
+  </si>
+  <si>
+    <t>**Passage:** The board's remuneration policy caps annual bonuses for executive directors at a percentage of base salary, but does not entitle directors to a bonus.
+**Statement:** Executive directors are guaranteed a bonus each year up to the cap.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where a contract loss is anticipated, the full anticipated loss is recognised immediately in the income statement.
+**Statement:** Anticipated contract losses are recognised at the point they become foreseeable rather than spread over the contract life.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where a covenant breach is remedied within the cure period, the issuer is treated as not having defaulted.
+**Statement:** A bond issuer who remedies a covenant breach within the cure period is in default.</t>
+  </si>
+  <si>
+    <t>**Passage:** Ships flying the flag of a regulated state must be recycled at approved facilities. Emergency recycling at non-listed facilities is permitted where the safety of the ship or crew is at risk, subject to notification of the authority within twenty-four hours.
+**Statement:** A ship may be recycled at a non-approved facility if the crew is in danger, provided the authority is notified promptly.</t>
+  </si>
+  <si>
+    <t>**Passage:** The licensing authority may issue, vary, or revoke licences. Minor variations to licence conditions may be made without a hearing.
+**Statement:** A minor variation to a licence requires a public hearing.</t>
   </si>
   <si>
     <t>**Passage:** Non-executive directors receive a fixed annual fee and are not eligible for bonuses or long-term incentive awards.
 **Statement:** A non-executive director may receive a long-term incentive award if performance targets are met.</t>
   </si>
   <si>
-    <t>**Passage:** The pension scheme has assets of £385 million and liabilities of £420 million.
-**Statement:** The pension scheme is currently in surplus.</t>
-  </si>
-  <si>
-    <t>**Passage:** Shareholder resolutions are categorised as ordinary, special, or unanimous. Ordinary resolutions require a simple majority. Special resolutions require approval from at least three-quarters of votes cast. Unanimous resolutions require the agreement of every shareholder.
-**Statement:** A resolution approved by every single shareholder qualifies as a special resolution.</t>
-  </si>
-  <si>
-    <t>**Passage:** Personal data breaches must be reported to the supervisory authority within 72 hours where they pose a risk to individuals' rights.
-**Statement:** Most data breaches occur due to human error.</t>
+    <t>**Passage:** VAT on imports is levied on the customs value plus duty, not on the customs value alone.
+**Statement:** VAT on imports is calculated solely on the customs value of the goods.</t>
+  </si>
+  <si>
+    <t>**Passage:** The licence may be transferred to another party only with the prior written consent of the licensor, which shall not be unreasonably withheld.
+**Statement:** A licensor cannot refuse transfer of the licence on arbitrary grounds.</t>
+  </si>
+  <si>
+    <t>**Passage:** Patients are triaged based on severity. Category 1 patients are seen immediately; Category 4 and 5 patients may wait longer, depending on demand.
+**Statement:** A Category 4 patient is always seen later than a Category 1 patient.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where a contract loss is anticipated, the full anticipated loss is recognised immediately in the income statement.
+**Statement:** Anticipated losses must be approved by the audit committee before being recognised.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 1 controlled drugs require a Home Office licence for any handling.
+**Statement:** The Home Office charges a fee for issuing Schedule 1 licences.</t>
   </si>
   <si>
     <t>**Passage:** Notification to affected individuals is required only where the breach poses a high risk to their rights and freedoms.
 **Statement:** A breach posing a medium risk must be notified to affected individuals.</t>
   </si>
   <si>
-    <t>**Passage:** Manufacturers are strictly liable for damage caused by defective products. Liability is capped at £5 million per product category per incident.
-**Statement:** A claimant must prove the manufacturer was negligent to succeed.</t>
-  </si>
-  <si>
-    <t>**Passage:** A development risks defence applies where the manufacturer can show the defect was undiscoverable given the scientific knowledge available at the time.
+    <t>**Passage:** The mortgage is offered at a variable rate linked to the lender's standard variable rate.
+**Statement:** Borrowers may switch to a fixed-rate mortgage at any time without a fee.</t>
+  </si>
+  <si>
+    <t>**Passage:** Failure to comply with consultation obligations may result in a protective award of up to ninety days' pay per affected employee.
+**Statement:** Non-compliance with consultation rules can lead to a financial award against the employer.</t>
+  </si>
+  <si>
+    <t>**Passage:** Vending machines are available on every floor of the building.
+**Statement:** Vending machines are restocked twice per week.</t>
+  </si>
+  <si>
+    <t>**Passage:** The patent licence grants exclusive rights in Europe and non-exclusive rights in Asia-Pacific.
+**Statement:** The licensee holds exclusive rights to the technology worldwide.</t>
+  </si>
+  <si>
+    <t>**Passage:** Anti-bribery policies prohibit facilitation payments even where they are customary or legally permitted locally.
+**Statement:** Breaches of the anti-bribery policy are referred to the local prosecutor.</t>
+  </si>
+  <si>
+    <t>**Passage:** Once a settlement agreement is in place, the employee may not bring a claim that has been the subject of the settlement.
+**Statement:** An employee bound by a settlement agreement is precluded from suing on the matters covered by it.</t>
+  </si>
+  <si>
+    <t>**Passage:** The professional standards committee may impose sanctions ranging from a written warning to permanent expulsion. The decision must be notified in writing within fourteen days of the hearing. An appeal may be lodged within thirty days of notification.
+**Statement:** A member who is expelled loses the right to appeal once thirty days have passed since notification.</t>
+  </si>
+  <si>
+    <t>**Passage:** Members of the professional body must complete continuing professional development each year. A defined minimum proportion must be structured learning.
+**Statement:** A member who completes only unstructured learning meets the annual CPD requirement.</t>
+  </si>
+  <si>
+    <t>**Passage:** Sickness absence of more than seven consecutive days requires a medical certificate.
+**Statement:** Returning to work after a long-term sickness absence requires a return-to-work interview.</t>
+  </si>
+  <si>
+    <t>**Passage:** Representative APRs must reflect the rate available to at least the majority of customers taking out the product.
+**Statement:** A representative APR may be based on the rate offered only to top-credit customers.</t>
+  </si>
+  <si>
+    <t>**Passage:** Where the contract has been in force for more than three years, an additional month of notice is required for termination without cause.
+**Statement:** Long-standing contracts attract a longer notice requirement for termination without cause than newer ones.</t>
+  </si>
+  <si>
+    <t>**Passage:** Reasonable hospitality is permitted provided it is recorded in the gifts register and does not exceed a defined value cap.
+**Statement:** Hospitality may be provided as long as the giver's intent is not corrupt.</t>
+  </si>
+  <si>
+    <t>**Passage:** The professional standards committee notifies its decision in writing within fourteen days of the hearing.
+**Statement:** Notifications include a reasoned explanation of the committee's findings.</t>
+  </si>
+  <si>
+    <t>**Passage:** In an insolvency, fixed charge holders are paid first, then insolvency expenses, then preferential creditors, then a prescribed portion to unsecured creditors, then floating charge holders.
+**Statement:** Insolvency expenses are paid before preferential creditors.</t>
+  </si>
+  <si>
+    <t>**Passage:** Permanent employees receive a fifteen per cent discount at the company's retail outlets.
+**Statement:** The fifteen per cent discount is also valid for online purchases.</t>
+  </si>
+  <si>
+    <t>**Passage:** The collective bargaining agreement requires thirty days' notice before any industrial action.
+**Statement:** Industrial action notices must be approved by a majority vote of union members.</t>
+  </si>
+  <si>
+    <t>**Passage:** CCTV footage is retained for thirty days before deletion.
+**Statement:** CCTV footage is stored on encrypted servers in a data centre.</t>
+  </si>
+  <si>
+    <t>**Passage:** Decennial liability insurance covers structural defects for ten years from completion.
+**Statement:** Decennial liability insurance premiums are paid annually by the contractor.</t>
+  </si>
+  <si>
+    <t>**Passage:** The drug's list price applies in high-income countries, while middle-income and low-income countries receive substantial discounts.
+**Statement:** Patients in high-income countries face a higher price than patients in low-income countries.</t>
+  </si>
+  <si>
+    <t>**Passage:** Holdings between the disclosure threshold and the substantial threshold must be disclosed to the company but are not made public.
+**Statement:** A shareholding above the disclosure threshold but below the substantial threshold is not visible to the market.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 2 controlled drugs require a full prescription written in ink, signed, and including the patient's name and address. Schedule 3 drugs require a prescription with less stringent rules.
+**Statement:** A prescription is required to dispense both Schedule 2 and Schedule 3 drugs.</t>
+  </si>
+  <si>
+    <t>**Passage:** Inventions created by academic staff in the course of their employment vest in the university. Revenue from commercialisation is split between the university and the inventor according to a tiered formula, with the university retaining a higher share at higher revenue levels.
+**Statement:** An inventor whose invention generates very high revenue receives a smaller proportion than the university.</t>
+  </si>
+  <si>
+    <t>**Passage:** A development risks defence applies where the manufacturer can show the defect was undiscoverable given the scientific knowledge available at the time the product was supplied.
 **Statement:** A defect that could not have been detected with the technology of the day may not result in liability.</t>
   </si>
   <si>
-    <t>**Passage:** Construction contract revenue is recognised using the percentage-of-completion method, based on costs incurred to date as a proportion of total estimated costs.
-**Statement:** Revenue is recognised in equal instalments over the contract life.</t>
-  </si>
-  <si>
-    <t>**Passage:** Where a contract loss is anticipated, the full anticipated loss is recognised immediately in the income statement.
-**Statement:** Anticipated losses are spread evenly over the remaining life of the contract.</t>
-  </si>
-  <si>
-    <t>**Passage:** The phase III trial has 90% statistical power to detect a 20% improvement in the primary endpoint, using a two-sided 5% significance level.
-**Statement:** A 20% improvement is the smallest difference the trial is designed to detect at 90% power.</t>
-  </si>
-  <si>
-    <t>**Passage:** Primary endpoint data is expected to be available approximately 24 months after enrolment is complete.
-**Statement:** The trial will be completed within four years of starting enrolment.</t>
-  </si>
-  <si>
-    <t>**Passage:** Tenancy deposits must be lodged with an approved deposit protection scheme within thirty days of receipt. Failure to comply may result in the tenant being awarded up to three times the deposit amount as compensation. The compensation award is at the court's discretion.
-**Statement:** A landlord who fails to protect a deposit will automatically pay three times the deposit as compensation.</t>
+    <t>**Passage:** Where the property is listed, separate listed building consent is required in addition to planning permission.
+**Statement:** Planning permission alone is sufficient to extend a listed building.</t>
+  </si>
+  <si>
+    <t>**Passage:** The cycle-to-work scheme operates through a salary sacrifice arrangement.
+**Statement:** The cycle scheme allows employees to spread the cost over eighteen months.</t>
+  </si>
+  <si>
+    <t>**Passage:** Tenancies of more than two years require long-form notice to terminate. For tenancies ending for development purposes, an additional period of notice on top of the standard requirement applies.
+**Statement:** A landlord ending a four-year tenancy for development purposes must give more notice than for a non-development termination.</t>
+  </si>
+  <si>
+    <t>**Passage:** Meeting room bookings must be made through the intranet portal at least twenty-four hours in advance.
+**Statement:** Meeting rooms can also be booked by telephone in urgent cases.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 1 drugs may not be possessed or supplied without a Home Office licence.
+**Statement:** Possessing a Schedule 1 drug without a Home Office licence is unlawful.</t>
+  </si>
+  <si>
+    <t>**Passage:** Schedule 1 drugs have no accepted medical use and require a Home Office licence for any handling.
+**Statement:** A pharmacist cannot supply a Schedule 1 drug to a patient under a normal NHS prescription.</t>
+  </si>
+  <si>
+    <t>**Passage:** Holdings below the disclosure threshold have no notification requirement.
+**Statement:** A small shareholder below the disclosure threshold need not inform anyone of their position.</t>
+  </si>
+  <si>
+    <t>**Passage:** Visa applications submitted in person are processed within two working weeks. Online applications are typically processed faster, except where additional documentation is requested, in which case the timeline restarts.
+**Statement:** An online application that triggers a documentation request will be completed within the original online processing time.</t>
+  </si>
+  <si>
+    <t>**Passage:** The training programme consists of three phases. Trainees must pass an assessment at the end of each phase before progressing. Failure to pass an assessment results in an extension to the relevant phase, after which the assessment is retaken.
+**Statement:** A trainee who fails the supervised practice assessment is dismissed from the programme.</t>
   </si>
   <si>
     <t>**Passage:** Goods originating from countries with a free trade agreement (FTA) attract a preferential rate of duty rather than the standard rate.
 **Statement:** FTA-origin goods are subject to a lower rate of duty than goods from non-FTA countries.</t>
   </si>
   <si>
-    <t>**Passage:** A settlement agreement between an employer and employee is binding only if the employee has received independent legal advice from a relevant adviser before signing.
-**Statement:** An employee who signs without legal advice is bound by the settlement.</t>
-  </si>
-  <si>
-    <t>**Passage:** Employers customarily contribute to the employee's legal fees, although this is not a legal requirement.
-**Statement:** The settlement bars the employee from working for competitors for 12 months.</t>
-  </si>
-  <si>
-    <t>**Passage:** Residential developments of 10 or more units must allocate 30% of units to affordable housing.
-**Statement:** A development of 8 units must include affordable housing.</t>
-  </si>
-  <si>
-    <t>**Passage:** Affordable housing contributions can be made on-site or as a financial contribution where on-site delivery is impracticable.
-**Statement:** Affordable housing must be provided as social rent rather than shared ownership.</t>
-  </si>
-  <si>
-    <t>**Passage:** Patients arriving at the urgent care centre are triaged based on the severity of their condition. Category 1 patients are seen immediately. Category 2 patients are seen within thirty minutes. Category 3 patients are seen within two hours. Category 4 and 5 patients may wait longer, depending on demand.
-**Statement:** A Category 3 patient is always seen sooner than a Category 4 patient.</t>
-  </si>
-  <si>
-    <t>**Passage:** A minimum score of 60 out of 100 is required for an investment-grade rating.
-**Statement:** A score of 58 results in an investment-grade rating.</t>
-  </si>
-  <si>
-    <t>**Passage:** Under the share incentive plan, shares awarded must be held in the plan for at least three years to retain the tax-free status.
-**Statement:** Shares withdrawn after four years still benefit from tax-free treatment.</t>
-  </si>
-  <si>
-    <t>**Passage:** Withdrawing shares within three years triggers income tax and national insurance on the market value at withdrawal.
-**Statement:** An employee withdrawing shares at 30 months will face an immediate tax charge.</t>
-  </si>
-  <si>
-    <t>**Passage:** An environmental permit is required for any installation emitting more than 20 tonnes of a regulated substance per year. Installations between 5 and 20 tonnes need only register.
-**Statement:** A 12-tonne emitter must hold a full environmental permit.</t>
-  </si>
-  <si>
-    <t>**Passage:** Installations emitting less than 5 tonnes are exempt from both permit and registration requirements.
-**Statement:** Failure to register an installation between 5 and 20 tonnes results in a fine.</t>
-  </si>
-  <si>
-    <t>**Passage:** First proven plagiarism offences result in a mark of zero for the affected assessment, with no resubmission allowed.
-**Statement:** A first plagiarism offence results in failure of the entire module.</t>
-  </si>
-  <si>
-    <t>**Passage:** Self-plagiarism — submitting the same work for two assessments — is treated as a first offence regardless of any prior record.
-**Statement:** A student with two prior offences who self-plagiarises will be expelled.</t>
-  </si>
-  <si>
-    <t>**Passage:** Construction contractors are liable for defects appearing within 12 months of practical completion. Latent defects may give rise to claims for up to six years under contract law.
-**Statement:** A latent defect found four years after completion may still give rise to contractor liability.</t>
-  </si>
-  <si>
-    <t>**Passage:** Decennial liability insurance covers structural defects for ten years from completion.
-**Statement:** Decennial liability premiums are paid annually by the contractor.</t>
-  </si>
-  <si>
-    <t>**Passage:** The contract may be terminated for cause by either party with immediate effect. Termination without cause requires three months' written notice. Where the contract has been in force for more than three years, an additional month of notice is required for termination without cause.
-**Statement:** A contract in its second year can be terminated without cause with three months' notice.</t>
-  </si>
-  <si>
-    <t>**Passage:** Members of the public attending a planning hearing may speak for up to three minutes each. Where multiple people wish to speak on the same item, the chair may direct that one representative speak on behalf of others. The total time allocated to public speaking on any single item is capped, with the cap set at the start of the hearing.
-**Statement:** Members of the public may always speak individually on every item.</t>
-  </si>
-  <si>
-    <t>**Passage:** Collective consultation is triggered when 20 or more redundancies are proposed within 90 days at a single establishment.
-**Statement:** A proposal to make 18 redundancies in 90 days requires collective consultation.</t>
-  </si>
-  <si>
-    <t>**Passage:** Where 100 or more redundancies are proposed, the minimum consultation period is 45 days. For 20–99 redundancies, the minimum is 30 days.
-**Statement:** 80 redundancies must be staggered over the consultation period.</t>
-  </si>
-  <si>
-    <t>**Passage:** The anti-bribery policy prohibits facilitation payments even where they are customary or legally permitted in the local jurisdiction.
-**Statement:** Facilitation payments are banned even in jurisdictions where they are lawful.</t>
-  </si>
-  <si>
-    <t>**Passage:** Reasonable hospitality is permitted provided it is recorded in the gifts register and does not exceed £75 in value.
-**Statement:** A £100 client lunch is acceptable under the policy if it is recorded in the gifts register.</t>
-  </si>
-  <si>
-    <t>**Passage:** The whistleblowing policy protects any worker who, in good faith, reports suspected wrongdoing through approved channels. Protections include immunity from disciplinary action and a right to remain anonymous. Reports made maliciously or in bad faith are not covered by these protections.
-**Statement:** A worker who maliciously fabricates an allegation is protected from disciplinary action.</t>
-  </si>
-  <si>
-    <t>**Passage:** When an abstraction licence lapses, abstraction must cease immediately and cannot resume until a new licence is granted.
-**Statement:** A licensee with a lapsed licence may continue abstracting while a renewal is pending.</t>
-  </si>
-  <si>
-    <t>**Passage:** The franchise grants exclusive rights for an initial five-year term. Renewal requires written notice at least six months before expiry.
-**Statement:** A franchisee giving four months' written notice loses the right to renew.</t>
-  </si>
-  <si>
-    <t>**Passage:** Renewal of the franchise is conditional on having met the performance benchmarks in Schedule 3 and not having committed any material breach in the previous 12 months.
-**Statement:** Meeting the performance benchmarks alone guarantees renewal.</t>
-  </si>
-  <si>
-    <t>**Passage:** Bond covenants require maintenance of a net leverage ratio not exceeding 4.0x. A breach triggers a 30-day cure period.
-**Statement:** Bondholders must hold their position for 12 months before they can vote on acceleration.</t>
-  </si>
-  <si>
-    <t>**Passage:** The licensing authority may issue, vary, or revoke licences. A revocation requires a public hearing where the licence holder may make representations. Minor variations to licence conditions may be made without a hearing, although the licence holder must be notified.
-**Statement:** A minor variation to a licence requires a public hearing.</t>
-  </si>
-  <si>
-    <t>**Passage:** Disputes are resolved first through informal discussion between the parties. If informal resolution fails, the matter is referred to mediation. Mediation must be attempted before any party initiates court proceedings, except where the dispute concerns urgent injunctive relief.
-**Statement:** A party seeking an emergency injunction may apply directly to the court without first attempting mediation.</t>
-  </si>
-  <si>
-    <t>**Passage:** The vehicle inspection scheme tests roadworthiness on three criteria: brakes, lights, and tyres. A vehicle that fails one criterion is issued a warning notice and given time to remedy the defect. A vehicle that fails two or more criteria simultaneously is impounded immediately.
-**Statement:** A vehicle with defective brakes alone will be impounded immediately.</t>
-  </si>
-  <si>
-    <t>**Passage:** Editorial decisions on news content are made by the editor-in-chief, in consultation with the news desk. Sponsored content is clearly labelled and is the responsibility of the commercial director. Where there is disagreement between the editorial and commercial functions, the publisher has final authority.
-**Statement:** The publisher has the final say on every piece of sponsored content that is published.</t>
-  </si>
-  <si>
-    <t>**Passage:** Underspent grant funds must be returned to the funder unless a no-cost extension is agreed in writing.
-**Statement:** Underspend returns must be made within 60 days of grant end.</t>
-  </si>
-  <si>
-    <t>**Passage:** Consumer credit advertisements must show the APR as prominently as any associated rate, where the advert includes any numerical interest or repayment figure.
-**Statement:** A credit advertisement containing only descriptive text and no numbers must show an APR.</t>
-  </si>
-  <si>
-    <t>**Passage:** Representative APRs must reflect the rate available to at least 51% of customers taking out the product.
-**Statement:** A representative APR may be based on the rate offered only to top-credit customers.</t>
-  </si>
-  <si>
-    <t>**Passage:** In an insolvency, fixed charge holders are paid first, then insolvency expenses, then preferential creditors, then a prescribed portion to unsecured creditors, then floating charge holders.
-**Statement:** Floating charge holders are paid before unsecured creditors.</t>
-  </si>
-  <si>
-    <t>**Passage:** Preferential creditors include employee arrears up to a statutory limit.
-**Statement:** All employee claims rank as preferential without limit.</t>
-  </si>
-  <si>
-    <t>**Passage:** Agricultural tenancies of more than two years require long-form notice to terminate. Where the landlord is recovering possession for development purposes, an additional period of notice on top of the standard requirement is required.
-**Statement:** A landlord ending a tenancy of any length for development purposes must give more notice than for a non-development termination.</t>
-  </si>
-  <si>
-    <t>**Passage:** Aviation accidents must be reported to the safety authority within 72 hours; lesser incidents within 21 days.
-**Statement:** Both accidents and serious incidents must be reported within 72 hours.</t>
-  </si>
-  <si>
-    <t>**Passage:** Operators must submit incident investigation findings to the authority within 90 days of the occurrence.
-**Statement:** Investigation findings have a three-month deadline.</t>
-  </si>
-  <si>
-    <t>**Passage:** Media plurality rules cap newspaper circulation share at 30% and television audience share at 25%.
-**Statement:** Fines for media plurality breaches are capped at 10% of annual revenue.</t>
-  </si>
-  <si>
-    <t>**Passage:** An entity that holds 28% of newspaper circulation and 26% of television audience share would breach media plurality regulations.
-**Statement:** The 25% TV audience cap is measured by total viewing hours.</t>
-  </si>
-  <si>
-    <t>**Passage:** Ships under 500 gross tonnage and ships used only in domestic waters are exempt from the approved-facility recycling requirement.
-**Statement:** A 600-tonne vessel operating internationally may be recycled at any facility.</t>
-  </si>
-  <si>
-    <t>**Passage:** Emergency recycling at non-listed facilities is permitted where the safety of the ship or crew is at risk, subject to notification within 24 hours.
-**Statement:** Emergency exception requires advance regulatory approval.</t>
-  </si>
-  <si>
-    <t>**Passage:** Schedule 1 controlled drugs may not be possessed or supplied without a Home Office licence.
-**Statement:** Schedule 1 drug research is funded primarily by government grants.</t>
-  </si>
-  <si>
-    <t>**Passage:** Schedule 2 drugs require a full prescription written in ink, signed, and including the patient's name and address. Schedule 3 drugs require a prescription with less stringent rules.
-**Statement:** A Schedule 3 drug can be dispensed without any prescription.</t>
-  </si>
-  <si>
-    <t>**Passage:** Shareholders holding a substantial stake are required to disclose their holding to the market. Holdings between the disclosure threshold and the substantial threshold must be disclosed to the company but not made public. Holdings below the disclosure threshold have no notification requirement.
-**Statement:** A shareholder with a holding above the substantial threshold may keep their position confidential.</t>
-  </si>
-  <si>
-    <t>**Passage:** After a right-to-buy purchase, discount repayment is on a sliding scale: 100% in year one, reducing by 20 percentage points each subsequent year.
-**Statement:** A buyer selling in year three repays 60% of the discount.</t>
-  </si>
-  <si>
-    <t>**Passage:** Workers who suffer an injury at work are entitled to statutory sick pay from the fourth day of absence. Pay continues until the worker is fit to return, subject to a statutory cap. Workers who recover sufficiently to return on light duties continue to receive sick pay if light duties cannot be accommodated.
-**Statement:** A worker absent for two days due to a workplace injury receives statutory sick pay.</t>
-  </si>
-  <si>
-    <t>**Passage:** Decommissioning funds are held in ring-fenced trusts and may not be used for any purpose other than decommissioning.
-**Statement:** The fund can be drawn upon to cover operational losses.</t>
-  </si>
-  <si>
-    <t>**Passage:** The training programme consists of three phases: induction, supervised practice, and independent practice. Trainees must pass a competency assessment at the end of each phase before progressing. Failure to pass an assessment results in an extension to the relevant phase, after which the assessment is retaken.
-**Statement:** A trainee who fails the supervised practice assessment is dismissed from the programme.</t>
-  </si>
-  <si>
-    <t>**Passage:** Permission for a residential extension is generally granted where the proposal complies with the local design code. Extensions in conservation areas require additional consideration of heritage impact. Where the property is listed, separate listed building consent is required in addition to planning permission.
-**Statement:** An extension to a listed property in a conservation area requires both listed building consent and consideration of heritage impact.</t>
-  </si>
-  <si>
-    <t>**Passage:** Members of the professional body must complete continuing professional development each year. A defined minimum proportion must be structured learning — formal courses, conferences, or assessed activities. The remaining hours may be unstructured.
-**Statement:** A member who completes only unstructured learning meets the annual CPD requirement.</t>
-  </si>
-  <si>
-    <t>**Passage:** Members completing more than 60 hours of CPD per year may carry forward up to 10 hours to the following year.
-**Statement:** A member completing exactly 60 hours can carry forward 10 hours.</t>
-  </si>
-  <si>
-    <t>**Passage:** Spectrum licences are awarded for an initial term of 20 years and may be renewed for a further 10 years subject to a spectrum efficiency review.
-**Statement:** A spectrum licensee operates for an initial term of two decades.</t>
-  </si>
-  <si>
-    <t>**Passage:** The spectrum efficiency review takes place two years before licence expiry.
-**Statement:** The review is conducted after the licence has expired.</t>
-  </si>
-  <si>
-    <t>**Passage:** Local authorities have a power, but not a duty, to undertake coastal protection works.
-**Statement:** Local authorities employ a coastal protection engineer at every coastal location.</t>
-  </si>
-  <si>
-    <t>**Passage:** Where a local authority undertakes coastal protection works, it may recover a portion of the cost from landowners whose property benefits from the works.
-**Statement:** A landowner whose property does not benefit from coastal works can be required to contribute to their cost.</t>
-  </si>
-  <si>
-    <t>**Passage:** Inventions created by academic staff in the course of their employment vest in the university.
-**Statement:** Academic staff personally own inventions they create as part of their job.</t>
-  </si>
-  <si>
-    <t>**Passage:** Inventions created by academic staff in the course of their employment vest in the university. Revenue from commercialisation is split between the university and the inventor according to a tiered formula, with the university retaining a higher share at higher revenue levels.
-**Statement:** An inventor whose invention generates very high revenue receives a smaller proportion than the university.</t>
-  </si>
-  <si>
-    <t>**Passage:** NHS goods and services contracts above £213,477 must follow public procurement regulations. Contracts below this threshold remain subject to the trust's internal financial procedures.
-**Statement:** The procurement threshold of £213,477 is updated every two years.</t>
-  </si>
-  <si>
-    <t>**Passage:** Splitting a contract artificially to fall below the procurement threshold is a breach regardless of individual contract values.
-**Statement:** Dividing a £400,000 contract into four £100,000 contracts to avoid procurement is permitted.</t>
-  </si>
-  <si>
-    <t>**Passage:** The mortgage is offered at a variable rate linked to the lender's standard variable rate, currently 5.75%. The lender may change the SVR with 30 days' written notice to the borrower.
-**Statement:** The lender can change the rate without informing the borrower.</t>
-  </si>
-  <si>
-    <t>**Passage:** The mortgage carries an early repayment charge of 2% of the outstanding balance if repaid in full within the first three years.
-**Statement:** A borrower repaying after four years would incur a 2% early repayment charge.</t>
-  </si>
-  <si>
-    <t>**Passage:** Anti-money laundering regulations require enhanced due diligence for transactions exceeding €15,000 with high-risk jurisdictions.
-**Statement:** A €20,000 transaction with a high-risk jurisdiction requires enhanced due diligence.</t>
-  </si>
-  <si>
-    <t>**Passage:** Politically exposed persons (PEPs) are subject to enhanced due diligence regardless of transaction size. PEPs include senior public officials, their immediate family members, and known close associates.
-**Statement:** A close associate of a senior public official is treated as a PEP for due diligence purposes.</t>
-  </si>
-  <si>
-    <t>**Passage:** The food labelling regulation requires energy values to be displayed in both kilojoules and kilocalories per 100g for all pre-packaged foods.
-**Statement:** All restaurants must display calorie counts on their menus.</t>
-  </si>
-  <si>
-    <t>**Passage:** Restaurants and cafés serving non-pre-packaged food are exempt from the food labelling regulation.
-**Statement:** A café selling pastries made on the premises must label energy values in kilojoules.</t>
-  </si>
-  <si>
-    <t>**Passage:** The collective bargaining agreement requires a 30-day notice period before any industrial action. Notice must specify the type of action and start date.
-**Statement:** A two-week notice of industrial action complies with the agreement.</t>
+    <t>**Passage:** The decision must be notified in writing within fourteen days of the hearing.
+**Statement:** A notification given orally would not satisfy the requirement.</t>
+  </si>
+  <si>
+    <t>**Passage:** Tenancy deposits must be lodged with an approved deposit protection scheme within thirty days of receipt.
+**Statement:** Approved deposit protection schemes are operated by independent trustees.</t>
   </si>
   <si>
     <t>True</t>
@@ -688,16 +1318,13 @@
     <t>Cannot Say</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>TRUE</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1072,22 +1699,22 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H2" t="s">
-        <v>194</v>
-      </c>
-      <c r="K2" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1095,22 +1722,22 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K3" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1118,22 +1745,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H4" t="s">
-        <v>195</v>
-      </c>
-      <c r="K4" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1141,22 +1768,22 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H5" t="s">
-        <v>195</v>
-      </c>
-      <c r="K5" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1164,22 +1791,22 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H6" t="s">
-        <v>195</v>
-      </c>
-      <c r="K6" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1187,22 +1814,22 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D7" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H7" t="s">
-        <v>194</v>
-      </c>
-      <c r="K7" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1210,22 +1837,22 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H8" t="s">
-        <v>195</v>
-      </c>
-      <c r="K8" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1233,22 +1860,22 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H9" t="s">
-        <v>195</v>
-      </c>
-      <c r="K9" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1256,22 +1883,22 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H10" t="s">
-        <v>195</v>
-      </c>
-      <c r="K10" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1279,22 +1906,22 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E11" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H11" t="s">
-        <v>196</v>
-      </c>
-      <c r="K11" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1302,22 +1929,22 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H12" t="s">
-        <v>194</v>
-      </c>
-      <c r="K12" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1325,22 +1952,22 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D13" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H13" t="s">
-        <v>195</v>
-      </c>
-      <c r="K13" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1348,22 +1975,22 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D14" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H14" t="s">
-        <v>195</v>
-      </c>
-      <c r="K14" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1371,22 +1998,22 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>204</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H15" t="s">
-        <v>196</v>
-      </c>
-      <c r="K15" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1394,22 +2021,22 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D16" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
-      </c>
-      <c r="K16" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1417,22 +2044,22 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D17" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H17" t="s">
-        <v>195</v>
-      </c>
-      <c r="K17" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1440,22 +2067,22 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H18" t="s">
-        <v>195</v>
-      </c>
-      <c r="K18" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1463,22 +2090,22 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>208</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D19" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E19" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H19" t="s">
-        <v>194</v>
-      </c>
-      <c r="K19" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1486,22 +2113,22 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H20" t="s">
-        <v>195</v>
-      </c>
-      <c r="K20" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1509,22 +2136,22 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D21" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H21" t="s">
-        <v>195</v>
-      </c>
-      <c r="K21" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1532,22 +2159,22 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H22" t="s">
-        <v>194</v>
-      </c>
-      <c r="K22" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1555,22 +2182,22 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D23" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H23" t="s">
-        <v>196</v>
-      </c>
-      <c r="K23" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1578,22 +2205,22 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D24" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H24" t="s">
-        <v>195</v>
-      </c>
-      <c r="K24" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1601,22 +2228,22 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D25" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H25" t="s">
-        <v>194</v>
-      </c>
-      <c r="K25" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1624,22 +2251,22 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D26" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E26" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H26" t="s">
-        <v>195</v>
-      </c>
-      <c r="K26" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1647,22 +2274,22 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D27" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H27" t="s">
-        <v>196</v>
-      </c>
-      <c r="K27" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1670,22 +2297,22 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D28" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H28" t="s">
-        <v>195</v>
-      </c>
-      <c r="K28" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1693,22 +2320,22 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D29" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H29" t="s">
-        <v>196</v>
-      </c>
-      <c r="K29" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1716,22 +2343,22 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D30" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E30" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H30" t="s">
-        <v>196</v>
-      </c>
-      <c r="K30" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1739,22 +2366,22 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D31" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H31" t="s">
-        <v>195</v>
-      </c>
-      <c r="K31" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1762,22 +2389,22 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D32" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E32" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H32" t="s">
-        <v>194</v>
-      </c>
-      <c r="K32" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1785,22 +2412,22 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E33" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H33" t="s">
-        <v>194</v>
-      </c>
-      <c r="K33" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1808,22 +2435,22 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>223</v>
       </c>
       <c r="C34" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D34" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E34" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H34" t="s">
-        <v>195</v>
-      </c>
-      <c r="K34" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1831,22 +2458,22 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D35" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H35" t="s">
-        <v>196</v>
-      </c>
-      <c r="K35" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1854,22 +2481,22 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H36" t="s">
-        <v>195</v>
-      </c>
-      <c r="K36" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1877,22 +2504,22 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D37" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H37" t="s">
-        <v>195</v>
-      </c>
-      <c r="K37" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1900,22 +2527,22 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="C38" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H38" t="s">
-        <v>194</v>
-      </c>
-      <c r="K38" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1923,22 +2550,22 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H39" t="s">
-        <v>196</v>
-      </c>
-      <c r="K39" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1946,22 +2573,22 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>229</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E40" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H40" t="s">
-        <v>194</v>
-      </c>
-      <c r="K40" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1969,22 +2596,22 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="C41" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D41" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E41" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H41" t="s">
-        <v>195</v>
-      </c>
-      <c r="K41" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -1992,22 +2619,22 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D42" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E42" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H42" t="s">
-        <v>195</v>
-      </c>
-      <c r="K42" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2015,22 +2642,22 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D43" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E43" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H43" t="s">
-        <v>196</v>
-      </c>
-      <c r="K43" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2038,22 +2665,22 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D44" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E44" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H44" t="s">
-        <v>194</v>
-      </c>
-      <c r="K44" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2061,22 +2688,22 @@
         <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>234</v>
       </c>
       <c r="C45" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D45" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H45" t="s">
-        <v>195</v>
-      </c>
-      <c r="K45" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2084,22 +2711,22 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D46" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E46" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H46" t="s">
-        <v>195</v>
-      </c>
-      <c r="K46" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2107,22 +2734,22 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>236</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D47" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E47" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H47" t="s">
-        <v>195</v>
-      </c>
-      <c r="K47" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2130,22 +2757,22 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D48" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E48" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H48" t="s">
-        <v>194</v>
-      </c>
-      <c r="K48" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2153,22 +2780,22 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D49" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E49" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H49" t="s">
-        <v>195</v>
-      </c>
-      <c r="K49" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2176,22 +2803,22 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E50" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H50" t="s">
-        <v>196</v>
-      </c>
-      <c r="K50" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2199,22 +2826,22 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C51" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D51" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E51" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H51" t="s">
-        <v>195</v>
-      </c>
-      <c r="K51" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2222,22 +2849,22 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E52" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H52" t="s">
-        <v>194</v>
-      </c>
-      <c r="K52" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2245,22 +2872,22 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>242</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D53" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E53" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H53" t="s">
-        <v>195</v>
-      </c>
-      <c r="K53" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2268,22 +2895,22 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>243</v>
       </c>
       <c r="C54" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D54" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E54" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H54" t="s">
-        <v>196</v>
-      </c>
-      <c r="K54" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2291,22 +2918,22 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D55" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H55" t="s">
-        <v>196</v>
-      </c>
-      <c r="K55" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2314,22 +2941,22 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="C56" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D56" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E56" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H56" t="s">
-        <v>195</v>
-      </c>
-      <c r="K56" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2337,22 +2964,22 @@
         <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="C57" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D57" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E57" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H57" t="s">
-        <v>195</v>
-      </c>
-      <c r="K57" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2360,22 +2987,22 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="C58" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D58" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E58" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H58" t="s">
-        <v>195</v>
-      </c>
-      <c r="K58" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2383,22 +3010,22 @@
         <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D59" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H59" t="s">
-        <v>195</v>
-      </c>
-      <c r="K59" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2406,22 +3033,22 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D60" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E60" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H60" t="s">
-        <v>196</v>
-      </c>
-      <c r="K60" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2429,22 +3056,22 @@
         <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="C61" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D61" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E61" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H61" t="s">
-        <v>196</v>
-      </c>
-      <c r="K61" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2452,22 +3079,22 @@
         <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D62" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E62" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H62" t="s">
-        <v>194</v>
-      </c>
-      <c r="K62" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2475,22 +3102,22 @@
         <v>72</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D63" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H63" t="s">
-        <v>196</v>
-      </c>
-      <c r="K63" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -2498,22 +3125,22 @@
         <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="C64" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D64" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E64" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H64" t="s">
-        <v>196</v>
-      </c>
-      <c r="K64" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -2521,22 +3148,22 @@
         <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="C65" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D65" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E65" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H65" t="s">
-        <v>195</v>
-      </c>
-      <c r="K65" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -2544,22 +3171,22 @@
         <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="C66" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D66" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E66" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H66" t="s">
-        <v>195</v>
-      </c>
-      <c r="K66" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -2567,22 +3194,22 @@
         <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D67" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E67" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H67" t="s">
-        <v>196</v>
-      </c>
-      <c r="K67" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K67" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -2590,22 +3217,22 @@
         <v>77</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="C68" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D68" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E68" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H68" t="s">
-        <v>195</v>
-      </c>
-      <c r="K68" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -2613,22 +3240,22 @@
         <v>78</v>
       </c>
       <c r="B69" t="s">
-        <v>168</v>
+        <v>258</v>
       </c>
       <c r="C69" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D69" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E69" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H69" t="s">
-        <v>195</v>
-      </c>
-      <c r="K69" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -2636,22 +3263,22 @@
         <v>79</v>
       </c>
       <c r="B70" t="s">
-        <v>169</v>
+        <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D70" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E70" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H70" t="s">
-        <v>194</v>
-      </c>
-      <c r="K70" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -2659,22 +3286,22 @@
         <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D71" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E71" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H71" t="s">
-        <v>195</v>
-      </c>
-      <c r="K71" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -2682,22 +3309,22 @@
         <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D72" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E72" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H72" t="s">
-        <v>195</v>
-      </c>
-      <c r="K72" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -2705,22 +3332,22 @@
         <v>82</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
+        <v>262</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D73" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E73" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H73" t="s">
-        <v>195</v>
-      </c>
-      <c r="K73" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -2728,22 +3355,22 @@
         <v>83</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D74" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E74" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H74" t="s">
-        <v>194</v>
-      </c>
-      <c r="K74" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -2751,22 +3378,22 @@
         <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="C75" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D75" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E75" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H75" t="s">
-        <v>195</v>
-      </c>
-      <c r="K75" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -2774,22 +3401,22 @@
         <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>265</v>
       </c>
       <c r="C76" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D76" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E76" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H76" t="s">
-        <v>195</v>
-      </c>
-      <c r="K76" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -2797,22 +3424,22 @@
         <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="C77" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D77" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E77" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H77" t="s">
-        <v>194</v>
-      </c>
-      <c r="K77" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -2820,22 +3447,22 @@
         <v>87</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>267</v>
       </c>
       <c r="C78" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D78" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E78" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H78" t="s">
-        <v>195</v>
-      </c>
-      <c r="K78" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -2843,22 +3470,22 @@
         <v>88</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>268</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D79" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E79" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H79" t="s">
-        <v>196</v>
-      </c>
-      <c r="K79" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -2866,22 +3493,22 @@
         <v>89</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="C80" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D80" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E80" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H80" t="s">
-        <v>195</v>
-      </c>
-      <c r="K80" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -2889,22 +3516,22 @@
         <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="C81" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D81" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E81" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H81" t="s">
-        <v>195</v>
-      </c>
-      <c r="K81" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -2912,22 +3539,22 @@
         <v>91</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="C82" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D82" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E82" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H82" t="s">
-        <v>194</v>
-      </c>
-      <c r="K82" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -2935,22 +3562,22 @@
         <v>92</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="C83" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D83" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E83" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H83" t="s">
-        <v>196</v>
-      </c>
-      <c r="K83" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -2958,22 +3585,22 @@
         <v>93</v>
       </c>
       <c r="B84" t="s">
-        <v>183</v>
+        <v>273</v>
       </c>
       <c r="C84" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D84" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E84" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H84" t="s">
-        <v>195</v>
-      </c>
-      <c r="K84" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -2981,22 +3608,22 @@
         <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>274</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D85" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E85" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H85" t="s">
-        <v>195</v>
-      </c>
-      <c r="K85" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3004,22 +3631,22 @@
         <v>95</v>
       </c>
       <c r="B86" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="C86" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E86" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H86" t="s">
-        <v>195</v>
-      </c>
-      <c r="K86" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3027,22 +3654,22 @@
         <v>96</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>276</v>
       </c>
       <c r="C87" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D87" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E87" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H87" t="s">
-        <v>194</v>
-      </c>
-      <c r="K87" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K87" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3050,22 +3677,22 @@
         <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="C88" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D88" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E88" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H88" t="s">
-        <v>194</v>
-      </c>
-      <c r="K88" t="s">
-        <v>197</v>
+        <v>375</v>
+      </c>
+      <c r="K88" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3073,22 +3700,22 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>188</v>
+        <v>278</v>
       </c>
       <c r="C89" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D89" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E89" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H89" t="s">
-        <v>196</v>
-      </c>
-      <c r="K89" t="s">
-        <v>197</v>
+        <v>376</v>
+      </c>
+      <c r="K89" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3096,22 +3723,22 @@
         <v>99</v>
       </c>
       <c r="B90" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="C90" t="s">
-        <v>191</v>
+        <v>371</v>
       </c>
       <c r="D90" t="s">
-        <v>192</v>
+        <v>372</v>
       </c>
       <c r="E90" t="s">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="H90" t="s">
-        <v>195</v>
-      </c>
-      <c r="K90" t="s">
-        <v>197</v>
+        <v>374</v>
+      </c>
+      <c r="K90" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3119,22 +3746,2092 @@
         <v>100</v>
       </c>
       <c r="B91" t="s">
+        <v>280</v>
+      </c>
+      <c r="C91" t="s">
+        <v>371</v>
+      </c>
+      <c r="D91" t="s">
+        <v>372</v>
+      </c>
+      <c r="E91" t="s">
+        <v>373</v>
+      </c>
+      <c r="H91" t="s">
+        <v>374</v>
+      </c>
+      <c r="K91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" t="s">
+        <v>281</v>
+      </c>
+      <c r="C92" t="s">
+        <v>371</v>
+      </c>
+      <c r="D92" t="s">
+        <v>372</v>
+      </c>
+      <c r="E92" t="s">
+        <v>373</v>
+      </c>
+      <c r="H92" t="s">
+        <v>374</v>
+      </c>
+      <c r="K92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" t="s">
+        <v>282</v>
+      </c>
+      <c r="C93" t="s">
+        <v>371</v>
+      </c>
+      <c r="D93" t="s">
+        <v>372</v>
+      </c>
+      <c r="E93" t="s">
+        <v>373</v>
+      </c>
+      <c r="H93" t="s">
+        <v>376</v>
+      </c>
+      <c r="K93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>103</v>
+      </c>
+      <c r="B94" t="s">
+        <v>283</v>
+      </c>
+      <c r="C94" t="s">
+        <v>371</v>
+      </c>
+      <c r="D94" t="s">
+        <v>372</v>
+      </c>
+      <c r="E94" t="s">
+        <v>373</v>
+      </c>
+      <c r="H94" t="s">
+        <v>376</v>
+      </c>
+      <c r="K94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>104</v>
+      </c>
+      <c r="B95" t="s">
+        <v>284</v>
+      </c>
+      <c r="C95" t="s">
+        <v>371</v>
+      </c>
+      <c r="D95" t="s">
+        <v>372</v>
+      </c>
+      <c r="E95" t="s">
+        <v>373</v>
+      </c>
+      <c r="H95" t="s">
+        <v>374</v>
+      </c>
+      <c r="K95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>105</v>
+      </c>
+      <c r="B96" t="s">
+        <v>285</v>
+      </c>
+      <c r="C96" t="s">
+        <v>371</v>
+      </c>
+      <c r="D96" t="s">
+        <v>372</v>
+      </c>
+      <c r="E96" t="s">
+        <v>373</v>
+      </c>
+      <c r="H96" t="s">
+        <v>374</v>
+      </c>
+      <c r="K96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>106</v>
+      </c>
+      <c r="B97" t="s">
+        <v>286</v>
+      </c>
+      <c r="C97" t="s">
+        <v>371</v>
+      </c>
+      <c r="D97" t="s">
+        <v>372</v>
+      </c>
+      <c r="E97" t="s">
+        <v>373</v>
+      </c>
+      <c r="H97" t="s">
+        <v>376</v>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>107</v>
+      </c>
+      <c r="B98" t="s">
+        <v>287</v>
+      </c>
+      <c r="C98" t="s">
+        <v>371</v>
+      </c>
+      <c r="D98" t="s">
+        <v>372</v>
+      </c>
+      <c r="E98" t="s">
+        <v>373</v>
+      </c>
+      <c r="H98" t="s">
+        <v>374</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>108</v>
+      </c>
+      <c r="B99" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" t="s">
+        <v>371</v>
+      </c>
+      <c r="D99" t="s">
+        <v>372</v>
+      </c>
+      <c r="E99" t="s">
+        <v>373</v>
+      </c>
+      <c r="H99" t="s">
+        <v>376</v>
+      </c>
+      <c r="K99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>109</v>
+      </c>
+      <c r="B100" t="s">
+        <v>289</v>
+      </c>
+      <c r="C100" t="s">
+        <v>371</v>
+      </c>
+      <c r="D100" t="s">
+        <v>372</v>
+      </c>
+      <c r="E100" t="s">
+        <v>373</v>
+      </c>
+      <c r="H100" t="s">
+        <v>376</v>
+      </c>
+      <c r="K100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>110</v>
+      </c>
+      <c r="B101" t="s">
+        <v>290</v>
+      </c>
+      <c r="C101" t="s">
+        <v>371</v>
+      </c>
+      <c r="D101" t="s">
+        <v>372</v>
+      </c>
+      <c r="E101" t="s">
+        <v>373</v>
+      </c>
+      <c r="H101" t="s">
+        <v>375</v>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>111</v>
+      </c>
+      <c r="B102" t="s">
+        <v>291</v>
+      </c>
+      <c r="C102" t="s">
+        <v>371</v>
+      </c>
+      <c r="D102" t="s">
+        <v>372</v>
+      </c>
+      <c r="E102" t="s">
+        <v>373</v>
+      </c>
+      <c r="H102" t="s">
+        <v>374</v>
+      </c>
+      <c r="K102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>112</v>
+      </c>
+      <c r="B103" t="s">
+        <v>292</v>
+      </c>
+      <c r="C103" t="s">
+        <v>371</v>
+      </c>
+      <c r="D103" t="s">
+        <v>372</v>
+      </c>
+      <c r="E103" t="s">
+        <v>373</v>
+      </c>
+      <c r="H103" t="s">
+        <v>376</v>
+      </c>
+      <c r="K103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" t="s">
+        <v>293</v>
+      </c>
+      <c r="C104" t="s">
+        <v>371</v>
+      </c>
+      <c r="D104" t="s">
+        <v>372</v>
+      </c>
+      <c r="E104" t="s">
+        <v>373</v>
+      </c>
+      <c r="H104" t="s">
+        <v>375</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" t="s">
+        <v>294</v>
+      </c>
+      <c r="C105" t="s">
+        <v>371</v>
+      </c>
+      <c r="D105" t="s">
+        <v>372</v>
+      </c>
+      <c r="E105" t="s">
+        <v>373</v>
+      </c>
+      <c r="H105" t="s">
+        <v>376</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" t="s">
+        <v>115</v>
+      </c>
+      <c r="B106" t="s">
+        <v>295</v>
+      </c>
+      <c r="C106" t="s">
+        <v>371</v>
+      </c>
+      <c r="D106" t="s">
+        <v>372</v>
+      </c>
+      <c r="E106" t="s">
+        <v>373</v>
+      </c>
+      <c r="H106" t="s">
+        <v>374</v>
+      </c>
+      <c r="K106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" t="s">
+        <v>116</v>
+      </c>
+      <c r="B107" t="s">
+        <v>296</v>
+      </c>
+      <c r="C107" t="s">
+        <v>371</v>
+      </c>
+      <c r="D107" t="s">
+        <v>372</v>
+      </c>
+      <c r="E107" t="s">
+        <v>373</v>
+      </c>
+      <c r="H107" t="s">
+        <v>376</v>
+      </c>
+      <c r="K107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" t="s">
+        <v>117</v>
+      </c>
+      <c r="B108" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" t="s">
+        <v>371</v>
+      </c>
+      <c r="D108" t="s">
+        <v>372</v>
+      </c>
+      <c r="E108" t="s">
+        <v>373</v>
+      </c>
+      <c r="H108" t="s">
+        <v>375</v>
+      </c>
+      <c r="K108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" t="s">
+        <v>298</v>
+      </c>
+      <c r="C109" t="s">
+        <v>371</v>
+      </c>
+      <c r="D109" t="s">
+        <v>372</v>
+      </c>
+      <c r="E109" t="s">
+        <v>373</v>
+      </c>
+      <c r="H109" t="s">
+        <v>376</v>
+      </c>
+      <c r="K109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" t="s">
+        <v>119</v>
+      </c>
+      <c r="B110" t="s">
+        <v>299</v>
+      </c>
+      <c r="C110" t="s">
+        <v>371</v>
+      </c>
+      <c r="D110" t="s">
+        <v>372</v>
+      </c>
+      <c r="E110" t="s">
+        <v>373</v>
+      </c>
+      <c r="H110" t="s">
+        <v>374</v>
+      </c>
+      <c r="K110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" t="s">
+        <v>120</v>
+      </c>
+      <c r="B111" t="s">
+        <v>300</v>
+      </c>
+      <c r="C111" t="s">
+        <v>371</v>
+      </c>
+      <c r="D111" t="s">
+        <v>372</v>
+      </c>
+      <c r="E111" t="s">
+        <v>373</v>
+      </c>
+      <c r="H111" t="s">
+        <v>375</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" t="s">
+        <v>301</v>
+      </c>
+      <c r="C112" t="s">
+        <v>371</v>
+      </c>
+      <c r="D112" t="s">
+        <v>372</v>
+      </c>
+      <c r="E112" t="s">
+        <v>373</v>
+      </c>
+      <c r="H112" t="s">
+        <v>375</v>
+      </c>
+      <c r="K112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" t="s">
+        <v>371</v>
+      </c>
+      <c r="D113" t="s">
+        <v>372</v>
+      </c>
+      <c r="E113" t="s">
+        <v>373</v>
+      </c>
+      <c r="H113" t="s">
+        <v>374</v>
+      </c>
+      <c r="K113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" t="s">
+        <v>303</v>
+      </c>
+      <c r="C114" t="s">
+        <v>371</v>
+      </c>
+      <c r="D114" t="s">
+        <v>372</v>
+      </c>
+      <c r="E114" t="s">
+        <v>373</v>
+      </c>
+      <c r="H114" t="s">
+        <v>375</v>
+      </c>
+      <c r="K114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" t="s">
+        <v>304</v>
+      </c>
+      <c r="C115" t="s">
+        <v>371</v>
+      </c>
+      <c r="D115" t="s">
+        <v>372</v>
+      </c>
+      <c r="E115" t="s">
+        <v>373</v>
+      </c>
+      <c r="H115" t="s">
+        <v>376</v>
+      </c>
+      <c r="K115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" t="s">
+        <v>305</v>
+      </c>
+      <c r="C116" t="s">
+        <v>371</v>
+      </c>
+      <c r="D116" t="s">
+        <v>372</v>
+      </c>
+      <c r="E116" t="s">
+        <v>373</v>
+      </c>
+      <c r="H116" t="s">
+        <v>376</v>
+      </c>
+      <c r="K116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" t="s">
+        <v>306</v>
+      </c>
+      <c r="C117" t="s">
+        <v>371</v>
+      </c>
+      <c r="D117" t="s">
+        <v>372</v>
+      </c>
+      <c r="E117" t="s">
+        <v>373</v>
+      </c>
+      <c r="H117" t="s">
+        <v>375</v>
+      </c>
+      <c r="K117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" t="s">
+        <v>307</v>
+      </c>
+      <c r="C118" t="s">
+        <v>371</v>
+      </c>
+      <c r="D118" t="s">
+        <v>372</v>
+      </c>
+      <c r="E118" t="s">
+        <v>373</v>
+      </c>
+      <c r="H118" t="s">
+        <v>374</v>
+      </c>
+      <c r="K118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" t="s">
+        <v>308</v>
+      </c>
+      <c r="C119" t="s">
+        <v>371</v>
+      </c>
+      <c r="D119" t="s">
+        <v>372</v>
+      </c>
+      <c r="E119" t="s">
+        <v>373</v>
+      </c>
+      <c r="H119" t="s">
+        <v>375</v>
+      </c>
+      <c r="K119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" t="s">
+        <v>309</v>
+      </c>
+      <c r="C120" t="s">
+        <v>371</v>
+      </c>
+      <c r="D120" t="s">
+        <v>372</v>
+      </c>
+      <c r="E120" t="s">
+        <v>373</v>
+      </c>
+      <c r="H120" t="s">
+        <v>375</v>
+      </c>
+      <c r="K120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" t="s">
+        <v>371</v>
+      </c>
+      <c r="D121" t="s">
+        <v>372</v>
+      </c>
+      <c r="E121" t="s">
+        <v>373</v>
+      </c>
+      <c r="H121" t="s">
+        <v>376</v>
+      </c>
+      <c r="K121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" t="s">
+        <v>311</v>
+      </c>
+      <c r="C122" t="s">
+        <v>371</v>
+      </c>
+      <c r="D122" t="s">
+        <v>372</v>
+      </c>
+      <c r="E122" t="s">
+        <v>373</v>
+      </c>
+      <c r="H122" t="s">
+        <v>374</v>
+      </c>
+      <c r="K122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" t="s">
+        <v>312</v>
+      </c>
+      <c r="C123" t="s">
+        <v>371</v>
+      </c>
+      <c r="D123" t="s">
+        <v>372</v>
+      </c>
+      <c r="E123" t="s">
+        <v>373</v>
+      </c>
+      <c r="H123" t="s">
+        <v>376</v>
+      </c>
+      <c r="K123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" t="s">
+        <v>313</v>
+      </c>
+      <c r="C124" t="s">
+        <v>371</v>
+      </c>
+      <c r="D124" t="s">
+        <v>372</v>
+      </c>
+      <c r="E124" t="s">
+        <v>373</v>
+      </c>
+      <c r="H124" t="s">
+        <v>375</v>
+      </c>
+      <c r="K124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" t="s">
+        <v>314</v>
+      </c>
+      <c r="C125" t="s">
+        <v>371</v>
+      </c>
+      <c r="D125" t="s">
+        <v>372</v>
+      </c>
+      <c r="E125" t="s">
+        <v>373</v>
+      </c>
+      <c r="H125" t="s">
+        <v>375</v>
+      </c>
+      <c r="K125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" t="s">
+        <v>315</v>
+      </c>
+      <c r="C126" t="s">
+        <v>371</v>
+      </c>
+      <c r="D126" t="s">
+        <v>372</v>
+      </c>
+      <c r="E126" t="s">
+        <v>373</v>
+      </c>
+      <c r="H126" t="s">
+        <v>376</v>
+      </c>
+      <c r="K126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" t="s">
+        <v>316</v>
+      </c>
+      <c r="C127" t="s">
+        <v>371</v>
+      </c>
+      <c r="D127" t="s">
+        <v>372</v>
+      </c>
+      <c r="E127" t="s">
+        <v>373</v>
+      </c>
+      <c r="H127" t="s">
+        <v>375</v>
+      </c>
+      <c r="K127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" t="s">
+        <v>317</v>
+      </c>
+      <c r="C128" t="s">
+        <v>371</v>
+      </c>
+      <c r="D128" t="s">
+        <v>372</v>
+      </c>
+      <c r="E128" t="s">
+        <v>373</v>
+      </c>
+      <c r="H128" t="s">
+        <v>376</v>
+      </c>
+      <c r="K128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
+        <v>318</v>
+      </c>
+      <c r="C129" t="s">
+        <v>371</v>
+      </c>
+      <c r="D129" t="s">
+        <v>372</v>
+      </c>
+      <c r="E129" t="s">
+        <v>373</v>
+      </c>
+      <c r="H129" t="s">
+        <v>374</v>
+      </c>
+      <c r="K129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" t="s">
+        <v>319</v>
+      </c>
+      <c r="C130" t="s">
+        <v>371</v>
+      </c>
+      <c r="D130" t="s">
+        <v>372</v>
+      </c>
+      <c r="E130" t="s">
+        <v>373</v>
+      </c>
+      <c r="H130" t="s">
+        <v>375</v>
+      </c>
+      <c r="K130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" t="s">
+        <v>320</v>
+      </c>
+      <c r="C131" t="s">
+        <v>371</v>
+      </c>
+      <c r="D131" t="s">
+        <v>372</v>
+      </c>
+      <c r="E131" t="s">
+        <v>373</v>
+      </c>
+      <c r="H131" t="s">
+        <v>375</v>
+      </c>
+      <c r="K131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" t="s">
+        <v>321</v>
+      </c>
+      <c r="C132" t="s">
+        <v>371</v>
+      </c>
+      <c r="D132" t="s">
+        <v>372</v>
+      </c>
+      <c r="E132" t="s">
+        <v>373</v>
+      </c>
+      <c r="H132" t="s">
+        <v>376</v>
+      </c>
+      <c r="K132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" t="s">
+        <v>322</v>
+      </c>
+      <c r="C133" t="s">
+        <v>371</v>
+      </c>
+      <c r="D133" t="s">
+        <v>372</v>
+      </c>
+      <c r="E133" t="s">
+        <v>373</v>
+      </c>
+      <c r="H133" t="s">
+        <v>376</v>
+      </c>
+      <c r="K133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" t="s">
+        <v>323</v>
+      </c>
+      <c r="C134" t="s">
+        <v>371</v>
+      </c>
+      <c r="D134" t="s">
+        <v>372</v>
+      </c>
+      <c r="E134" t="s">
+        <v>373</v>
+      </c>
+      <c r="H134" t="s">
+        <v>375</v>
+      </c>
+      <c r="K134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" t="s">
+        <v>324</v>
+      </c>
+      <c r="C135" t="s">
+        <v>371</v>
+      </c>
+      <c r="D135" t="s">
+        <v>372</v>
+      </c>
+      <c r="E135" t="s">
+        <v>373</v>
+      </c>
+      <c r="H135" t="s">
+        <v>376</v>
+      </c>
+      <c r="K135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" t="s">
+        <v>325</v>
+      </c>
+      <c r="C136" t="s">
+        <v>371</v>
+      </c>
+      <c r="D136" t="s">
+        <v>372</v>
+      </c>
+      <c r="E136" t="s">
+        <v>373</v>
+      </c>
+      <c r="H136" t="s">
+        <v>375</v>
+      </c>
+      <c r="K136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" t="s">
+        <v>326</v>
+      </c>
+      <c r="C137" t="s">
+        <v>371</v>
+      </c>
+      <c r="D137" t="s">
+        <v>372</v>
+      </c>
+      <c r="E137" t="s">
+        <v>373</v>
+      </c>
+      <c r="H137" t="s">
+        <v>376</v>
+      </c>
+      <c r="K137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" t="s">
+        <v>327</v>
+      </c>
+      <c r="C138" t="s">
+        <v>371</v>
+      </c>
+      <c r="D138" t="s">
+        <v>372</v>
+      </c>
+      <c r="E138" t="s">
+        <v>373</v>
+      </c>
+      <c r="H138" t="s">
+        <v>375</v>
+      </c>
+      <c r="K138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" t="s">
+        <v>328</v>
+      </c>
+      <c r="C139" t="s">
+        <v>371</v>
+      </c>
+      <c r="D139" t="s">
+        <v>372</v>
+      </c>
+      <c r="E139" t="s">
+        <v>373</v>
+      </c>
+      <c r="H139" t="s">
+        <v>376</v>
+      </c>
+      <c r="K139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" t="s">
+        <v>329</v>
+      </c>
+      <c r="C140" t="s">
+        <v>371</v>
+      </c>
+      <c r="D140" t="s">
+        <v>372</v>
+      </c>
+      <c r="E140" t="s">
+        <v>373</v>
+      </c>
+      <c r="H140" t="s">
+        <v>376</v>
+      </c>
+      <c r="K140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" t="s">
+        <v>330</v>
+      </c>
+      <c r="C141" t="s">
+        <v>371</v>
+      </c>
+      <c r="D141" t="s">
+        <v>372</v>
+      </c>
+      <c r="E141" t="s">
+        <v>373</v>
+      </c>
+      <c r="H141" t="s">
+        <v>376</v>
+      </c>
+      <c r="K141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" t="s">
+        <v>331</v>
+      </c>
+      <c r="C142" t="s">
+        <v>371</v>
+      </c>
+      <c r="D142" t="s">
+        <v>372</v>
+      </c>
+      <c r="E142" t="s">
+        <v>373</v>
+      </c>
+      <c r="H142" t="s">
+        <v>375</v>
+      </c>
+      <c r="K142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" t="s">
+        <v>332</v>
+      </c>
+      <c r="C143" t="s">
+        <v>371</v>
+      </c>
+      <c r="D143" t="s">
+        <v>372</v>
+      </c>
+      <c r="E143" t="s">
+        <v>373</v>
+      </c>
+      <c r="H143" t="s">
+        <v>376</v>
+      </c>
+      <c r="K143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" t="s">
+        <v>333</v>
+      </c>
+      <c r="C144" t="s">
+        <v>371</v>
+      </c>
+      <c r="D144" t="s">
+        <v>372</v>
+      </c>
+      <c r="E144" t="s">
+        <v>373</v>
+      </c>
+      <c r="H144" t="s">
+        <v>374</v>
+      </c>
+      <c r="K144" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" t="s">
+        <v>334</v>
+      </c>
+      <c r="C145" t="s">
+        <v>371</v>
+      </c>
+      <c r="D145" t="s">
+        <v>372</v>
+      </c>
+      <c r="E145" t="s">
+        <v>373</v>
+      </c>
+      <c r="H145" t="s">
+        <v>374</v>
+      </c>
+      <c r="K145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" t="s">
+        <v>335</v>
+      </c>
+      <c r="C146" t="s">
+        <v>371</v>
+      </c>
+      <c r="D146" t="s">
+        <v>372</v>
+      </c>
+      <c r="E146" t="s">
+        <v>373</v>
+      </c>
+      <c r="H146" t="s">
+        <v>376</v>
+      </c>
+      <c r="K146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" t="s">
+        <v>336</v>
+      </c>
+      <c r="C147" t="s">
+        <v>371</v>
+      </c>
+      <c r="D147" t="s">
+        <v>372</v>
+      </c>
+      <c r="E147" t="s">
+        <v>373</v>
+      </c>
+      <c r="H147" t="s">
+        <v>374</v>
+      </c>
+      <c r="K147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" t="s">
+        <v>337</v>
+      </c>
+      <c r="C148" t="s">
+        <v>371</v>
+      </c>
+      <c r="D148" t="s">
+        <v>372</v>
+      </c>
+      <c r="E148" t="s">
+        <v>373</v>
+      </c>
+      <c r="H148" t="s">
+        <v>375</v>
+      </c>
+      <c r="K148" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" t="s">
+        <v>158</v>
+      </c>
+      <c r="B149" t="s">
+        <v>338</v>
+      </c>
+      <c r="C149" t="s">
+        <v>371</v>
+      </c>
+      <c r="D149" t="s">
+        <v>372</v>
+      </c>
+      <c r="E149" t="s">
+        <v>373</v>
+      </c>
+      <c r="H149" t="s">
+        <v>374</v>
+      </c>
+      <c r="K149" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" t="s">
+        <v>339</v>
+      </c>
+      <c r="C150" t="s">
+        <v>371</v>
+      </c>
+      <c r="D150" t="s">
+        <v>372</v>
+      </c>
+      <c r="E150" t="s">
+        <v>373</v>
+      </c>
+      <c r="H150" t="s">
+        <v>376</v>
+      </c>
+      <c r="K150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" t="s">
+        <v>340</v>
+      </c>
+      <c r="C151" t="s">
+        <v>371</v>
+      </c>
+      <c r="D151" t="s">
+        <v>372</v>
+      </c>
+      <c r="E151" t="s">
+        <v>373</v>
+      </c>
+      <c r="H151" t="s">
+        <v>374</v>
+      </c>
+      <c r="K151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+      <c r="B152" t="s">
+        <v>341</v>
+      </c>
+      <c r="C152" t="s">
+        <v>371</v>
+      </c>
+      <c r="D152" t="s">
+        <v>372</v>
+      </c>
+      <c r="E152" t="s">
+        <v>373</v>
+      </c>
+      <c r="H152" t="s">
+        <v>375</v>
+      </c>
+      <c r="K152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" t="s">
+        <v>342</v>
+      </c>
+      <c r="C153" t="s">
+        <v>371</v>
+      </c>
+      <c r="D153" t="s">
+        <v>372</v>
+      </c>
+      <c r="E153" t="s">
+        <v>373</v>
+      </c>
+      <c r="H153" t="s">
+        <v>375</v>
+      </c>
+      <c r="K153" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+      <c r="B154" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" t="s">
+        <v>371</v>
+      </c>
+      <c r="D154" t="s">
+        <v>372</v>
+      </c>
+      <c r="E154" t="s">
+        <v>373</v>
+      </c>
+      <c r="H154" t="s">
+        <v>376</v>
+      </c>
+      <c r="K154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155" t="s">
+        <v>164</v>
+      </c>
+      <c r="B155" t="s">
+        <v>344</v>
+      </c>
+      <c r="C155" t="s">
+        <v>371</v>
+      </c>
+      <c r="D155" t="s">
+        <v>372</v>
+      </c>
+      <c r="E155" t="s">
+        <v>373</v>
+      </c>
+      <c r="H155" t="s">
+        <v>374</v>
+      </c>
+      <c r="K155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156" t="s">
+        <v>165</v>
+      </c>
+      <c r="B156" t="s">
+        <v>345</v>
+      </c>
+      <c r="C156" t="s">
+        <v>371</v>
+      </c>
+      <c r="D156" t="s">
+        <v>372</v>
+      </c>
+      <c r="E156" t="s">
+        <v>373</v>
+      </c>
+      <c r="H156" t="s">
+        <v>376</v>
+      </c>
+      <c r="K156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" t="s">
+        <v>346</v>
+      </c>
+      <c r="C157" t="s">
+        <v>371</v>
+      </c>
+      <c r="D157" t="s">
+        <v>372</v>
+      </c>
+      <c r="E157" t="s">
+        <v>373</v>
+      </c>
+      <c r="H157" t="s">
+        <v>375</v>
+      </c>
+      <c r="K157" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="A158" t="s">
+        <v>167</v>
+      </c>
+      <c r="B158" t="s">
+        <v>347</v>
+      </c>
+      <c r="C158" t="s">
+        <v>371</v>
+      </c>
+      <c r="D158" t="s">
+        <v>372</v>
+      </c>
+      <c r="E158" t="s">
+        <v>373</v>
+      </c>
+      <c r="H158" t="s">
+        <v>376</v>
+      </c>
+      <c r="K158" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="A159" t="s">
+        <v>168</v>
+      </c>
+      <c r="B159" t="s">
+        <v>348</v>
+      </c>
+      <c r="C159" t="s">
+        <v>371</v>
+      </c>
+      <c r="D159" t="s">
+        <v>372</v>
+      </c>
+      <c r="E159" t="s">
+        <v>373</v>
+      </c>
+      <c r="H159" t="s">
+        <v>374</v>
+      </c>
+      <c r="K159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="A160" t="s">
+        <v>169</v>
+      </c>
+      <c r="B160" t="s">
+        <v>349</v>
+      </c>
+      <c r="C160" t="s">
+        <v>371</v>
+      </c>
+      <c r="D160" t="s">
+        <v>372</v>
+      </c>
+      <c r="E160" t="s">
+        <v>373</v>
+      </c>
+      <c r="H160" t="s">
+        <v>375</v>
+      </c>
+      <c r="K160" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="A161" t="s">
+        <v>170</v>
+      </c>
+      <c r="B161" t="s">
+        <v>350</v>
+      </c>
+      <c r="C161" t="s">
+        <v>371</v>
+      </c>
+      <c r="D161" t="s">
+        <v>372</v>
+      </c>
+      <c r="E161" t="s">
+        <v>373</v>
+      </c>
+      <c r="H161" t="s">
+        <v>374</v>
+      </c>
+      <c r="K161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="A162" t="s">
+        <v>171</v>
+      </c>
+      <c r="B162" t="s">
+        <v>351</v>
+      </c>
+      <c r="C162" t="s">
+        <v>371</v>
+      </c>
+      <c r="D162" t="s">
+        <v>372</v>
+      </c>
+      <c r="E162" t="s">
+        <v>373</v>
+      </c>
+      <c r="H162" t="s">
+        <v>374</v>
+      </c>
+      <c r="K162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="A163" t="s">
+        <v>172</v>
+      </c>
+      <c r="B163" t="s">
+        <v>352</v>
+      </c>
+      <c r="C163" t="s">
+        <v>371</v>
+      </c>
+      <c r="D163" t="s">
+        <v>372</v>
+      </c>
+      <c r="E163" t="s">
+        <v>373</v>
+      </c>
+      <c r="H163" t="s">
+        <v>374</v>
+      </c>
+      <c r="K163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" t="s">
+        <v>173</v>
+      </c>
+      <c r="B164" t="s">
+        <v>353</v>
+      </c>
+      <c r="C164" t="s">
+        <v>371</v>
+      </c>
+      <c r="D164" t="s">
+        <v>372</v>
+      </c>
+      <c r="E164" t="s">
+        <v>373</v>
+      </c>
+      <c r="H164" t="s">
+        <v>374</v>
+      </c>
+      <c r="K164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="A165" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" t="s">
+        <v>354</v>
+      </c>
+      <c r="C165" t="s">
+        <v>371</v>
+      </c>
+      <c r="D165" t="s">
+        <v>372</v>
+      </c>
+      <c r="E165" t="s">
+        <v>373</v>
+      </c>
+      <c r="H165" t="s">
+        <v>375</v>
+      </c>
+      <c r="K165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" t="s">
+        <v>175</v>
+      </c>
+      <c r="B166" t="s">
+        <v>355</v>
+      </c>
+      <c r="C166" t="s">
+        <v>371</v>
+      </c>
+      <c r="D166" t="s">
+        <v>372</v>
+      </c>
+      <c r="E166" t="s">
+        <v>373</v>
+      </c>
+      <c r="H166" t="s">
+        <v>375</v>
+      </c>
+      <c r="K166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+      <c r="B167" t="s">
+        <v>356</v>
+      </c>
+      <c r="C167" t="s">
+        <v>371</v>
+      </c>
+      <c r="D167" t="s">
+        <v>372</v>
+      </c>
+      <c r="E167" t="s">
+        <v>373</v>
+      </c>
+      <c r="H167" t="s">
+        <v>375</v>
+      </c>
+      <c r="K167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="A168" t="s">
+        <v>177</v>
+      </c>
+      <c r="B168" t="s">
+        <v>357</v>
+      </c>
+      <c r="C168" t="s">
+        <v>371</v>
+      </c>
+      <c r="D168" t="s">
+        <v>372</v>
+      </c>
+      <c r="E168" t="s">
+        <v>373</v>
+      </c>
+      <c r="H168" t="s">
+        <v>375</v>
+      </c>
+      <c r="K168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169" t="s">
+        <v>358</v>
+      </c>
+      <c r="C169" t="s">
+        <v>371</v>
+      </c>
+      <c r="D169" t="s">
+        <v>372</v>
+      </c>
+      <c r="E169" t="s">
+        <v>373</v>
+      </c>
+      <c r="H169" t="s">
+        <v>375</v>
+      </c>
+      <c r="K169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" t="s">
+        <v>179</v>
+      </c>
+      <c r="B170" t="s">
+        <v>359</v>
+      </c>
+      <c r="C170" t="s">
+        <v>371</v>
+      </c>
+      <c r="D170" t="s">
+        <v>372</v>
+      </c>
+      <c r="E170" t="s">
+        <v>373</v>
+      </c>
+      <c r="H170" t="s">
+        <v>376</v>
+      </c>
+      <c r="K170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" t="s">
+        <v>180</v>
+      </c>
+      <c r="B171" t="s">
+        <v>360</v>
+      </c>
+      <c r="C171" t="s">
+        <v>371</v>
+      </c>
+      <c r="D171" t="s">
+        <v>372</v>
+      </c>
+      <c r="E171" t="s">
+        <v>373</v>
+      </c>
+      <c r="H171" t="s">
+        <v>374</v>
+      </c>
+      <c r="K171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" t="s">
+        <v>181</v>
+      </c>
+      <c r="B172" t="s">
+        <v>361</v>
+      </c>
+      <c r="C172" t="s">
+        <v>371</v>
+      </c>
+      <c r="D172" t="s">
+        <v>372</v>
+      </c>
+      <c r="E172" t="s">
+        <v>373</v>
+      </c>
+      <c r="H172" t="s">
+        <v>375</v>
+      </c>
+      <c r="K172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" t="s">
+        <v>182</v>
+      </c>
+      <c r="B173" t="s">
+        <v>362</v>
+      </c>
+      <c r="C173" t="s">
+        <v>371</v>
+      </c>
+      <c r="D173" t="s">
+        <v>372</v>
+      </c>
+      <c r="E173" t="s">
+        <v>373</v>
+      </c>
+      <c r="H173" t="s">
+        <v>374</v>
+      </c>
+      <c r="K173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>183</v>
+      </c>
+      <c r="B174" t="s">
+        <v>363</v>
+      </c>
+      <c r="C174" t="s">
+        <v>371</v>
+      </c>
+      <c r="D174" t="s">
+        <v>372</v>
+      </c>
+      <c r="E174" t="s">
+        <v>373</v>
+      </c>
+      <c r="H174" t="s">
+        <v>375</v>
+      </c>
+      <c r="K174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>184</v>
+      </c>
+      <c r="B175" t="s">
+        <v>364</v>
+      </c>
+      <c r="C175" t="s">
+        <v>371</v>
+      </c>
+      <c r="D175" t="s">
+        <v>372</v>
+      </c>
+      <c r="E175" t="s">
+        <v>373</v>
+      </c>
+      <c r="H175" t="s">
+        <v>375</v>
+      </c>
+      <c r="K175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>185</v>
+      </c>
+      <c r="B176" t="s">
+        <v>365</v>
+      </c>
+      <c r="C176" t="s">
+        <v>371</v>
+      </c>
+      <c r="D176" t="s">
+        <v>372</v>
+      </c>
+      <c r="E176" t="s">
+        <v>373</v>
+      </c>
+      <c r="H176" t="s">
+        <v>375</v>
+      </c>
+      <c r="K176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" t="s">
+        <v>186</v>
+      </c>
+      <c r="B177" t="s">
+        <v>366</v>
+      </c>
+      <c r="C177" t="s">
+        <v>371</v>
+      </c>
+      <c r="D177" t="s">
+        <v>372</v>
+      </c>
+      <c r="E177" t="s">
+        <v>373</v>
+      </c>
+      <c r="H177" t="s">
+        <v>376</v>
+      </c>
+      <c r="K177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" t="s">
+        <v>187</v>
+      </c>
+      <c r="B178" t="s">
+        <v>367</v>
+      </c>
+      <c r="C178" t="s">
+        <v>371</v>
+      </c>
+      <c r="D178" t="s">
+        <v>372</v>
+      </c>
+      <c r="E178" t="s">
+        <v>373</v>
+      </c>
+      <c r="H178" t="s">
+        <v>376</v>
+      </c>
+      <c r="K178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" t="s">
+        <v>188</v>
+      </c>
+      <c r="B179" t="s">
+        <v>368</v>
+      </c>
+      <c r="C179" t="s">
+        <v>371</v>
+      </c>
+      <c r="D179" t="s">
+        <v>372</v>
+      </c>
+      <c r="E179" t="s">
+        <v>373</v>
+      </c>
+      <c r="H179" t="s">
+        <v>375</v>
+      </c>
+      <c r="K179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" t="s">
+        <v>189</v>
+      </c>
+      <c r="B180" t="s">
+        <v>369</v>
+      </c>
+      <c r="C180" t="s">
+        <v>371</v>
+      </c>
+      <c r="D180" t="s">
+        <v>372</v>
+      </c>
+      <c r="E180" t="s">
+        <v>373</v>
+      </c>
+      <c r="H180" t="s">
+        <v>375</v>
+      </c>
+      <c r="K180" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" t="s">
         <v>190</v>
       </c>
-      <c r="C91" t="s">
-        <v>191</v>
-      </c>
-      <c r="D91" t="s">
-        <v>192</v>
-      </c>
-      <c r="E91" t="s">
-        <v>193</v>
-      </c>
-      <c r="H91" t="s">
-        <v>195</v>
-      </c>
-      <c r="K91" t="s">
-        <v>197</v>
+      <c r="B181" t="s">
+        <v>370</v>
+      </c>
+      <c r="C181" t="s">
+        <v>371</v>
+      </c>
+      <c r="D181" t="s">
+        <v>372</v>
+      </c>
+      <c r="E181" t="s">
+        <v>373</v>
+      </c>
+      <c r="H181" t="s">
+        <v>374</v>
+      </c>
+      <c r="K181" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
